--- a/research/traditional_assets/database/data/serbia/serbia_engineering_construction.xlsx
+++ b/research/traditional_assets/database/data/serbia/serbia_engineering_construction.xlsx
@@ -1278,7 +1278,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1415,22 +1415,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.1106379453799011</v>
+        <v>0.1105102384618312</v>
       </c>
       <c r="C2">
-        <v>24.49729882113324</v>
+        <v>24.28940900271923</v>
       </c>
       <c r="D2">
-        <v>23.73029882113324</v>
+        <v>23.75540900271923</v>
       </c>
       <c r="E2">
-        <v>-7.9</v>
+        <v>-7.667000000000001</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>0.233</v>
       </c>
       <c r="G2">
         <v>0.767</v>
@@ -1451,28 +1451,28 @@
         <v>3.467499999999999</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.0117199</v>
       </c>
       <c r="N2">
-        <v>3.467499999999999</v>
+        <v>3.455780099999999</v>
       </c>
       <c r="O2">
-        <v>0.5201249999999998</v>
+        <v>0.5183670149999998</v>
       </c>
       <c r="P2">
-        <v>2.947375</v>
+        <v>2.937413084999999</v>
       </c>
       <c r="Q2">
-        <v>4.067375</v>
+        <v>4.057413084999999</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.1106379453799011</v>
+        <v>0.1111946348099305</v>
       </c>
       <c r="T2">
-        <v>0.7767418785034671</v>
+        <v>0.7834108744300119</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1489,7 +1489,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>295.86429918344</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1497,22 +1497,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.1105102384618312</v>
+        <v>0.1103825315437614</v>
       </c>
       <c r="C3">
-        <v>24.28940900271923</v>
+        <v>24.08157238120054</v>
       </c>
       <c r="D3">
-        <v>23.75540900271923</v>
+        <v>23.78057238120054</v>
       </c>
       <c r="E3">
-        <v>-7.667000000000001</v>
+        <v>-7.434</v>
       </c>
       <c r="F3">
-        <v>0.233</v>
+        <v>0.466</v>
       </c>
       <c r="G3">
         <v>0.767</v>
@@ -1533,28 +1533,28 @@
         <v>3.467499999999999</v>
       </c>
       <c r="M3">
-        <v>0.0117199</v>
+        <v>0.0234398</v>
       </c>
       <c r="N3">
-        <v>3.455780099999999</v>
+        <v>3.4440602</v>
       </c>
       <c r="O3">
-        <v>0.5183670149999998</v>
+        <v>0.5166090299999999</v>
       </c>
       <c r="P3">
-        <v>2.937413084999999</v>
+        <v>2.927451169999999</v>
       </c>
       <c r="Q3">
-        <v>4.057413084999999</v>
+        <v>4.04745117</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.1111946348099305</v>
+        <v>0.1117626852487361</v>
       </c>
       <c r="T3">
-        <v>0.7834108744300119</v>
+        <v>0.7902159723142416</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1571,7 +1571,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>295.86429918344</v>
+        <v>147.93214959172</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1579,22 +1579,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.1103825315437614</v>
+        <v>0.1102548246256915</v>
       </c>
       <c r="C4">
-        <v>24.08157238120054</v>
+        <v>23.87378912580595</v>
       </c>
       <c r="D4">
-        <v>23.78057238120054</v>
+        <v>23.80578912580595</v>
       </c>
       <c r="E4">
-        <v>-7.434</v>
+        <v>-7.201000000000001</v>
       </c>
       <c r="F4">
-        <v>0.466</v>
+        <v>0.699</v>
       </c>
       <c r="G4">
         <v>0.767</v>
@@ -1615,28 +1615,28 @@
         <v>3.467499999999999</v>
       </c>
       <c r="M4">
-        <v>0.0234398</v>
+        <v>0.0351597</v>
       </c>
       <c r="N4">
-        <v>3.4440602</v>
+        <v>3.432340299999999</v>
       </c>
       <c r="O4">
-        <v>0.5166090299999999</v>
+        <v>0.5148510449999999</v>
       </c>
       <c r="P4">
-        <v>2.927451169999999</v>
+        <v>2.917489255</v>
       </c>
       <c r="Q4">
-        <v>4.04745117</v>
+        <v>4.037489255</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.1117626852487361</v>
+        <v>0.1123424480677232</v>
       </c>
       <c r="T4">
-        <v>0.7902159723142416</v>
+        <v>0.797161381495053</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1653,7 +1653,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>147.93214959172</v>
+        <v>98.6214330611467</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1661,22 +1661,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.1102548246256915</v>
+        <v>0.1101271177076216</v>
       </c>
       <c r="C5">
-        <v>23.87378912580595</v>
+        <v>23.66605940648284</v>
       </c>
       <c r="D5">
-        <v>23.80578912580595</v>
+        <v>23.83105940648284</v>
       </c>
       <c r="E5">
-        <v>-7.201000000000001</v>
+        <v>-6.968</v>
       </c>
       <c r="F5">
-        <v>0.699</v>
+        <v>0.9320000000000001</v>
       </c>
       <c r="G5">
         <v>0.767</v>
@@ -1697,28 +1697,28 @@
         <v>3.467499999999999</v>
       </c>
       <c r="M5">
-        <v>0.0351597</v>
+        <v>0.0468796</v>
       </c>
       <c r="N5">
-        <v>3.432340299999999</v>
+        <v>3.420620399999999</v>
       </c>
       <c r="O5">
-        <v>0.5148510449999999</v>
+        <v>0.5130930599999999</v>
       </c>
       <c r="P5">
-        <v>2.917489255</v>
+        <v>2.90752734</v>
       </c>
       <c r="Q5">
-        <v>4.037489255</v>
+        <v>4.02752734</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.1123424480677232</v>
+        <v>0.1129342892787726</v>
       </c>
       <c r="T5">
-        <v>0.797161381495053</v>
+        <v>0.8042514867004649</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1735,7 +1735,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>98.6214330611467</v>
+        <v>73.96607479586002</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1743,22 +1743,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.1101271177076216</v>
+        <v>0.1099994107895518</v>
       </c>
       <c r="C6">
-        <v>23.66605940648284</v>
+        <v>23.45838339390091</v>
       </c>
       <c r="D6">
-        <v>23.83105940648284</v>
+        <v>23.85638339390091</v>
       </c>
       <c r="E6">
-        <v>-6.968</v>
+        <v>-6.735</v>
       </c>
       <c r="F6">
-        <v>0.9320000000000001</v>
+        <v>1.165</v>
       </c>
       <c r="G6">
         <v>0.767</v>
@@ -1779,28 +1779,28 @@
         <v>3.467499999999999</v>
       </c>
       <c r="M6">
-        <v>0.0468796</v>
+        <v>0.0585995</v>
       </c>
       <c r="N6">
-        <v>3.420620399999999</v>
+        <v>3.408900499999999</v>
       </c>
       <c r="O6">
-        <v>0.5130930599999999</v>
+        <v>0.5113350749999999</v>
       </c>
       <c r="P6">
-        <v>2.90752734</v>
+        <v>2.897565424999999</v>
       </c>
       <c r="Q6">
-        <v>4.02752734</v>
+        <v>4.017565424999999</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.1129342892787726</v>
+        <v>0.1135385903047914</v>
       </c>
       <c r="T6">
-        <v>0.8042514867004649</v>
+        <v>0.8114908572786222</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1817,7 +1817,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>73.96607479586002</v>
+        <v>59.17285983668801</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1825,22 +1825,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.1099994107895518</v>
+        <v>0.1098717038714819</v>
       </c>
       <c r="C7">
-        <v>23.45838339390091</v>
+        <v>23.25076125945612</v>
       </c>
       <c r="D7">
-        <v>23.85638339390091</v>
+        <v>23.88176125945612</v>
       </c>
       <c r="E7">
-        <v>-6.735</v>
+        <v>-6.502000000000001</v>
       </c>
       <c r="F7">
-        <v>1.165</v>
+        <v>1.398</v>
       </c>
       <c r="G7">
         <v>0.767</v>
@@ -1861,28 +1861,28 @@
         <v>3.467499999999999</v>
       </c>
       <c r="M7">
-        <v>0.0585995</v>
+        <v>0.0703194</v>
       </c>
       <c r="N7">
-        <v>3.408900499999999</v>
+        <v>3.3971806</v>
       </c>
       <c r="O7">
-        <v>0.5113350749999999</v>
+        <v>0.50957709</v>
       </c>
       <c r="P7">
-        <v>2.897565424999999</v>
+        <v>2.887603509999999</v>
       </c>
       <c r="Q7">
-        <v>4.017565424999999</v>
+        <v>4.007603509999999</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.1135385903047914</v>
+        <v>0.1141557487994489</v>
       </c>
       <c r="T7">
-        <v>0.8114908572786222</v>
+        <v>0.8188842570180168</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1899,7 +1899,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>59.17285983668801</v>
+        <v>49.31071653057334</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1907,22 +1907,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.1098717038714819</v>
+        <v>0.1097439969534121</v>
       </c>
       <c r="C8">
-        <v>23.25076125945612</v>
+        <v>23.04319317527448</v>
       </c>
       <c r="D8">
-        <v>23.88176125945612</v>
+        <v>23.90719317527448</v>
       </c>
       <c r="E8">
-        <v>-6.502000000000001</v>
+        <v>-6.269</v>
       </c>
       <c r="F8">
-        <v>1.398</v>
+        <v>1.631</v>
       </c>
       <c r="G8">
         <v>0.767</v>
@@ -1943,28 +1943,28 @@
         <v>3.467499999999999</v>
       </c>
       <c r="M8">
-        <v>0.07031939999999999</v>
+        <v>0.08203929999999998</v>
       </c>
       <c r="N8">
-        <v>3.3971806</v>
+        <v>3.385460699999999</v>
       </c>
       <c r="O8">
-        <v>0.50957709</v>
+        <v>0.5078191049999999</v>
       </c>
       <c r="P8">
-        <v>2.887603509999999</v>
+        <v>2.877641595</v>
       </c>
       <c r="Q8">
-        <v>4.007603509999999</v>
+        <v>3.997641595</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.1141557487994489</v>
+        <v>0.114786179519798</v>
       </c>
       <c r="T8">
-        <v>0.8188842570180168</v>
+        <v>0.8264366546012696</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1981,7 +1981,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>49.31071653057336</v>
+        <v>42.26632845477717</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1989,22 +1989,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.1097439969534121</v>
+        <v>0.1096162900353423</v>
       </c>
       <c r="C9">
-        <v>23.04319317527448</v>
+        <v>22.83567931421602</v>
       </c>
       <c r="D9">
-        <v>23.90719317527448</v>
+        <v>23.93267931421602</v>
       </c>
       <c r="E9">
-        <v>-6.269</v>
+        <v>-6.036</v>
       </c>
       <c r="F9">
-        <v>1.631</v>
+        <v>1.864</v>
       </c>
       <c r="G9">
         <v>0.767</v>
@@ -2025,28 +2025,28 @@
         <v>3.467499999999999</v>
       </c>
       <c r="M9">
-        <v>0.08203930000000001</v>
+        <v>0.0937592</v>
       </c>
       <c r="N9">
-        <v>3.385460699999999</v>
+        <v>3.373740799999999</v>
       </c>
       <c r="O9">
-        <v>0.5078191049999999</v>
+        <v>0.5060611199999999</v>
       </c>
       <c r="P9">
-        <v>2.877641595</v>
+        <v>2.867679679999999</v>
       </c>
       <c r="Q9">
-        <v>3.997641595</v>
+        <v>3.987679679999999</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.114786179519798</v>
+        <v>0.1154303152558068</v>
       </c>
       <c r="T9">
-        <v>0.8264366546012696</v>
+        <v>0.8341532347406799</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2063,7 +2063,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>42.26632845477715</v>
+        <v>36.98303739793001</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2071,22 +2071,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.1096162900353423</v>
+        <v>0.1094885831172724</v>
       </c>
       <c r="C10">
-        <v>22.83567931421602</v>
+        <v>22.62821984987863</v>
       </c>
       <c r="D10">
-        <v>23.93267931421602</v>
+        <v>23.95821984987863</v>
       </c>
       <c r="E10">
-        <v>-6.036</v>
+        <v>-5.803000000000001</v>
       </c>
       <c r="F10">
-        <v>1.864</v>
+        <v>2.097</v>
       </c>
       <c r="G10">
         <v>0.767</v>
@@ -2107,28 +2107,28 @@
         <v>3.467499999999999</v>
       </c>
       <c r="M10">
-        <v>0.0937592</v>
+        <v>0.1054791</v>
       </c>
       <c r="N10">
-        <v>3.373740799999999</v>
+        <v>3.362020899999999</v>
       </c>
       <c r="O10">
-        <v>0.5060611199999999</v>
+        <v>0.5043031349999999</v>
       </c>
       <c r="P10">
-        <v>2.867679679999999</v>
+        <v>2.857717764999999</v>
       </c>
       <c r="Q10">
-        <v>3.987679679999999</v>
+        <v>3.977717765</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.1154303152558068</v>
+        <v>0.1160886078211785</v>
       </c>
       <c r="T10">
-        <v>0.8341532347406799</v>
+        <v>0.8420394100479893</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2145,7 +2145,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>36.98303739793001</v>
+        <v>32.87381102038223</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2153,22 +2153,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.1094885831172724</v>
+        <v>0.1093608761992026</v>
       </c>
       <c r="C11">
-        <v>22.62821984987863</v>
+        <v>22.42081495660204</v>
       </c>
       <c r="D11">
-        <v>23.95821984987863</v>
+        <v>23.98381495660204</v>
       </c>
       <c r="E11">
-        <v>-5.803000000000001</v>
+        <v>-5.57</v>
       </c>
       <c r="F11">
-        <v>2.097</v>
+        <v>2.33</v>
       </c>
       <c r="G11">
         <v>0.767</v>
@@ -2189,28 +2189,28 @@
         <v>3.467499999999999</v>
       </c>
       <c r="M11">
-        <v>0.1054791</v>
+        <v>0.117199</v>
       </c>
       <c r="N11">
-        <v>3.362020899999999</v>
+        <v>3.350301</v>
       </c>
       <c r="O11">
-        <v>0.5043031349999999</v>
+        <v>0.5025451499999999</v>
       </c>
       <c r="P11">
-        <v>2.857717764999999</v>
+        <v>2.84775585</v>
       </c>
       <c r="Q11">
-        <v>3.977717765</v>
+        <v>3.96775585</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.1160886078211785</v>
+        <v>0.1167615291102251</v>
       </c>
       <c r="T11">
-        <v>0.8420394100479893</v>
+        <v>0.8501008336954613</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2227,7 +2227,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>32.87381102038223</v>
+        <v>29.58642991834401</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2235,22 +2235,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.1093608761992026</v>
+        <v>0.1092331692811327</v>
       </c>
       <c r="C12">
-        <v>22.42081495660204</v>
+        <v>22.21346480947178</v>
       </c>
       <c r="D12">
-        <v>23.98381495660204</v>
+        <v>24.00946480947178</v>
       </c>
       <c r="E12">
-        <v>-5.57</v>
+        <v>-5.337</v>
       </c>
       <c r="F12">
-        <v>2.33</v>
+        <v>2.563</v>
       </c>
       <c r="G12">
         <v>0.767</v>
@@ -2271,28 +2271,28 @@
         <v>3.467499999999999</v>
       </c>
       <c r="M12">
-        <v>0.117199</v>
+        <v>0.1289189</v>
       </c>
       <c r="N12">
-        <v>3.350301</v>
+        <v>3.338581099999999</v>
       </c>
       <c r="O12">
-        <v>0.5025451499999999</v>
+        <v>0.5007871649999999</v>
       </c>
       <c r="P12">
-        <v>2.84775585</v>
+        <v>2.837793935</v>
       </c>
       <c r="Q12">
-        <v>3.96775585</v>
+        <v>3.957793935</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.1167615291102251</v>
+        <v>0.1174495722259918</v>
       </c>
       <c r="T12">
-        <v>0.8501008336954613</v>
+        <v>0.8583434129305167</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2309,7 +2309,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>29.58642991834401</v>
+        <v>26.89675447122183</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2317,22 +2317,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.1092331692811327</v>
+        <v>0.1091054623630628</v>
       </c>
       <c r="C13">
-        <v>22.21346480947178</v>
+        <v>22.0061695843232</v>
       </c>
       <c r="D13">
-        <v>24.00946480947178</v>
+        <v>24.0351695843232</v>
       </c>
       <c r="E13">
-        <v>-5.337</v>
+        <v>-5.104000000000001</v>
       </c>
       <c r="F13">
-        <v>2.563</v>
+        <v>2.796</v>
       </c>
       <c r="G13">
         <v>0.767</v>
@@ -2353,28 +2353,28 @@
         <v>3.467499999999999</v>
       </c>
       <c r="M13">
-        <v>0.1289189</v>
+        <v>0.1406388</v>
       </c>
       <c r="N13">
-        <v>3.338581099999999</v>
+        <v>3.326861199999999</v>
       </c>
       <c r="O13">
-        <v>0.5007871649999999</v>
+        <v>0.4990291799999999</v>
       </c>
       <c r="P13">
-        <v>2.837793935</v>
+        <v>2.827832019999999</v>
       </c>
       <c r="Q13">
-        <v>3.957793935</v>
+        <v>3.947832019999999</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.1174495722259918</v>
+        <v>0.1181532526852987</v>
       </c>
       <c r="T13">
-        <v>0.8583434129305167</v>
+        <v>0.8667733235118236</v>
       </c>
       <c r="U13">
         <v>0.0503</v>
@@ -2391,7 +2391,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>26.89675447122183</v>
+        <v>24.65535826528668</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2399,22 +2399,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.1091054623630628</v>
+        <v>0.108977755444993</v>
       </c>
       <c r="C14">
-        <v>22.0061695843232</v>
+        <v>21.7989294577454</v>
       </c>
       <c r="D14">
-        <v>24.0351695843232</v>
+        <v>24.0609294577454</v>
       </c>
       <c r="E14">
-        <v>-5.104000000000001</v>
+        <v>-4.871</v>
       </c>
       <c r="F14">
-        <v>2.796</v>
+        <v>3.029</v>
       </c>
       <c r="G14">
         <v>0.767</v>
@@ -2435,28 +2435,28 @@
         <v>3.467499999999999</v>
       </c>
       <c r="M14">
-        <v>0.1406388</v>
+        <v>0.1523587</v>
       </c>
       <c r="N14">
-        <v>3.326861199999999</v>
+        <v>3.315141299999999</v>
       </c>
       <c r="O14">
-        <v>0.4990291799999999</v>
+        <v>0.4972711949999998</v>
       </c>
       <c r="P14">
-        <v>2.827832019999999</v>
+        <v>2.817870104999999</v>
       </c>
       <c r="Q14">
-        <v>3.947832019999999</v>
+        <v>3.937870105</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.1181532526852987</v>
+        <v>0.1188731097068885</v>
       </c>
       <c r="T14">
-        <v>0.8667733235118236</v>
+        <v>0.8753970251409764</v>
       </c>
       <c r="U14">
         <v>0.0503</v>
@@ -2473,7 +2473,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>24.65535826528668</v>
+        <v>22.75879224488</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2481,22 +2481,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.108977755444993</v>
+        <v>0.1088500485269231</v>
       </c>
       <c r="C15">
-        <v>21.7989294577454</v>
+        <v>21.59174460708541</v>
       </c>
       <c r="D15">
-        <v>24.0609294577454</v>
+        <v>24.08674460708541</v>
       </c>
       <c r="E15">
-        <v>-4.871</v>
+        <v>-4.638</v>
       </c>
       <c r="F15">
-        <v>3.029</v>
+        <v>3.262</v>
       </c>
       <c r="G15">
         <v>0.767</v>
@@ -2517,28 +2517,28 @@
         <v>3.467499999999999</v>
       </c>
       <c r="M15">
-        <v>0.1523587</v>
+        <v>0.1640786</v>
       </c>
       <c r="N15">
-        <v>3.315141299999999</v>
+        <v>3.3034214</v>
       </c>
       <c r="O15">
-        <v>0.4972711949999998</v>
+        <v>0.4955132099999999</v>
       </c>
       <c r="P15">
-        <v>2.817870104999999</v>
+        <v>2.80790819</v>
       </c>
       <c r="Q15">
-        <v>3.937870105</v>
+        <v>3.92790819</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.1188731097068885</v>
+        <v>0.1196097075894455</v>
       </c>
       <c r="T15">
-        <v>0.8753970251409764</v>
+        <v>0.8842212779708072</v>
       </c>
       <c r="U15">
         <v>0.0503</v>
@@ -2555,7 +2555,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>22.75879224488</v>
+        <v>21.13316422738858</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2563,22 +2563,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.1088500485269231</v>
+        <v>0.1087223416088533</v>
       </c>
       <c r="C16">
-        <v>21.59174460708541</v>
+        <v>21.38461521045211</v>
       </c>
       <c r="D16">
-        <v>24.08674460708541</v>
+        <v>24.11261521045212</v>
       </c>
       <c r="E16">
-        <v>-4.638</v>
+        <v>-4.404999999999999</v>
       </c>
       <c r="F16">
-        <v>3.262</v>
+        <v>3.495000000000001</v>
       </c>
       <c r="G16">
         <v>0.767</v>
@@ -2599,28 +2599,28 @@
         <v>3.467499999999999</v>
       </c>
       <c r="M16">
-        <v>0.1640786</v>
+        <v>0.1757985</v>
       </c>
       <c r="N16">
-        <v>3.3034214</v>
+        <v>3.291701499999999</v>
       </c>
       <c r="O16">
-        <v>0.4955132099999999</v>
+        <v>0.4937552249999999</v>
       </c>
       <c r="P16">
-        <v>2.80790819</v>
+        <v>2.797946274999999</v>
       </c>
       <c r="Q16">
-        <v>3.92790819</v>
+        <v>3.917946274999999</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.1196097075894455</v>
+        <v>0.1203636371868862</v>
       </c>
       <c r="T16">
-        <v>0.8842212779708072</v>
+        <v>0.893253160278987</v>
       </c>
       <c r="U16">
         <v>0.0503</v>
@@ -2637,7 +2637,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>21.13316422738858</v>
+        <v>19.72428661222933</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2645,22 +2645,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.1087223416088533</v>
+        <v>0.1085946346907835</v>
       </c>
       <c r="C17">
-        <v>21.38461521045211</v>
+        <v>21.17754144672048</v>
       </c>
       <c r="D17">
-        <v>24.11261521045212</v>
+        <v>24.13854144672048</v>
       </c>
       <c r="E17">
-        <v>-4.405</v>
+        <v>-4.172000000000001</v>
       </c>
       <c r="F17">
-        <v>3.495</v>
+        <v>3.728</v>
       </c>
       <c r="G17">
         <v>0.767</v>
@@ -2681,28 +2681,28 @@
         <v>3.467499999999999</v>
       </c>
       <c r="M17">
-        <v>0.1757985</v>
+        <v>0.1875184</v>
       </c>
       <c r="N17">
-        <v>3.291701499999999</v>
+        <v>3.279981599999999</v>
       </c>
       <c r="O17">
-        <v>0.4937552249999999</v>
+        <v>0.4919972399999999</v>
       </c>
       <c r="P17">
-        <v>2.797946274999999</v>
+        <v>2.787984359999999</v>
       </c>
       <c r="Q17">
-        <v>3.917946274999999</v>
+        <v>3.907984359999999</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.1203636371868862</v>
+        <v>0.1211355174890279</v>
       </c>
       <c r="T17">
-        <v>0.893253160278987</v>
+        <v>0.9025000874040285</v>
       </c>
       <c r="U17">
         <v>0.0503</v>
@@ -2719,7 +2719,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>19.72428661222934</v>
+        <v>18.491518698965</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2727,22 +2727,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.1085946346907835</v>
+        <v>0.1084669277727136</v>
       </c>
       <c r="C18">
-        <v>21.17754144672048</v>
+        <v>20.97052349553558</v>
       </c>
       <c r="D18">
-        <v>24.13854144672048</v>
+        <v>24.16452349553558</v>
       </c>
       <c r="E18">
-        <v>-4.172000000000001</v>
+        <v>-3.939</v>
       </c>
       <c r="F18">
-        <v>3.728</v>
+        <v>3.961</v>
       </c>
       <c r="G18">
         <v>0.767</v>
@@ -2763,28 +2763,28 @@
         <v>3.467499999999999</v>
       </c>
       <c r="M18">
-        <v>0.1875184</v>
+        <v>0.1992383</v>
       </c>
       <c r="N18">
-        <v>3.279981599999999</v>
+        <v>3.268261699999999</v>
       </c>
       <c r="O18">
-        <v>0.4919972399999999</v>
+        <v>0.4902392549999999</v>
       </c>
       <c r="P18">
-        <v>2.787984359999999</v>
+        <v>2.778022445</v>
       </c>
       <c r="Q18">
-        <v>3.907984359999999</v>
+        <v>3.898022445</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.1211355174890279</v>
+        <v>0.1219259973165224</v>
       </c>
       <c r="T18">
-        <v>0.9025000874040285</v>
+        <v>0.911969832050155</v>
       </c>
       <c r="U18">
         <v>0.0503</v>
@@ -2801,7 +2801,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>18.491518698965</v>
+        <v>17.40378230490824</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2809,22 +2809,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.1084669277727136</v>
+        <v>0.1083392208546437</v>
       </c>
       <c r="C19">
-        <v>20.97052349553558</v>
+        <v>20.76356153731679</v>
       </c>
       <c r="D19">
-        <v>24.16452349553558</v>
+        <v>24.19056153731679</v>
       </c>
       <c r="E19">
-        <v>-3.939</v>
+        <v>-3.706</v>
       </c>
       <c r="F19">
-        <v>3.961</v>
+        <v>4.194000000000001</v>
       </c>
       <c r="G19">
         <v>0.767</v>
@@ -2845,28 +2845,28 @@
         <v>3.467499999999999</v>
       </c>
       <c r="M19">
-        <v>0.1992383</v>
+        <v>0.2109582</v>
       </c>
       <c r="N19">
-        <v>3.268261699999999</v>
+        <v>3.256541799999999</v>
       </c>
       <c r="O19">
-        <v>0.4902392549999999</v>
+        <v>0.4884812699999999</v>
       </c>
       <c r="P19">
-        <v>2.778022445</v>
+        <v>2.76806053</v>
       </c>
       <c r="Q19">
-        <v>3.898022445</v>
+        <v>3.88806053</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.1219259973165224</v>
+        <v>0.1227357571398094</v>
       </c>
       <c r="T19">
-        <v>0.911969832050155</v>
+        <v>0.9216705460778944</v>
       </c>
       <c r="U19">
         <v>0.0503</v>
@@ -2883,7 +2883,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>17.40378230490824</v>
+        <v>16.43690551019111</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2891,22 +2891,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.1083392208546438</v>
+        <v>0.1082115139365739</v>
       </c>
       <c r="C20">
-        <v>20.76356153731679</v>
+        <v>20.55665575326196</v>
       </c>
       <c r="D20">
-        <v>24.19056153731679</v>
+        <v>24.21665575326196</v>
       </c>
       <c r="E20">
-        <v>-3.706</v>
+        <v>-3.473</v>
       </c>
       <c r="F20">
-        <v>4.194</v>
+        <v>4.427</v>
       </c>
       <c r="G20">
         <v>0.767</v>
@@ -2927,28 +2927,28 @@
         <v>3.467499999999999</v>
       </c>
       <c r="M20">
-        <v>0.2109582</v>
+        <v>0.2226781</v>
       </c>
       <c r="N20">
-        <v>3.256541799999999</v>
+        <v>3.244821899999999</v>
       </c>
       <c r="O20">
-        <v>0.4884812699999999</v>
+        <v>0.4867232849999999</v>
       </c>
       <c r="P20">
-        <v>2.76806053</v>
+        <v>2.758098614999999</v>
       </c>
       <c r="Q20">
-        <v>3.88806053</v>
+        <v>3.878098614999999</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.1227357571398094</v>
+        <v>0.1235655110328073</v>
       </c>
       <c r="T20">
-        <v>0.9216705460778944</v>
+        <v>0.9316107839087879</v>
       </c>
       <c r="U20">
         <v>0.0503</v>
@@ -2965,7 +2965,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>16.43690551019112</v>
+        <v>15.57180522018106</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2973,22 +2973,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.1082115139365739</v>
+        <v>0.108083807018504</v>
       </c>
       <c r="C21">
-        <v>20.55665575326196</v>
+        <v>20.34980632535162</v>
       </c>
       <c r="D21">
-        <v>24.21665575326196</v>
+        <v>24.24280632535162</v>
       </c>
       <c r="E21">
-        <v>-3.473</v>
+        <v>-3.24</v>
       </c>
       <c r="F21">
-        <v>4.427</v>
+        <v>4.66</v>
       </c>
       <c r="G21">
         <v>0.767</v>
@@ -3009,28 +3009,28 @@
         <v>3.467499999999999</v>
       </c>
       <c r="M21">
-        <v>0.2226781</v>
+        <v>0.234398</v>
       </c>
       <c r="N21">
-        <v>3.244821899999999</v>
+        <v>3.233101999999999</v>
       </c>
       <c r="O21">
-        <v>0.4867232849999999</v>
+        <v>0.4849652999999999</v>
       </c>
       <c r="P21">
-        <v>2.758098614999999</v>
+        <v>2.748136699999999</v>
       </c>
       <c r="Q21">
-        <v>3.878098614999999</v>
+        <v>3.8681367</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.1235655110328073</v>
+        <v>0.1244160087731301</v>
       </c>
       <c r="T21">
-        <v>0.9316107839087879</v>
+        <v>0.9417995276854538</v>
       </c>
       <c r="U21">
         <v>0.0503</v>
@@ -3047,7 +3047,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>15.57180522018106</v>
+        <v>14.793214959172</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3055,22 +3055,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.108083807018504</v>
+        <v>0.1079561001004342</v>
       </c>
       <c r="C22">
-        <v>20.34980632535162</v>
+        <v>20.14301343635316</v>
       </c>
       <c r="D22">
-        <v>24.24280632535162</v>
+        <v>24.26901343635317</v>
       </c>
       <c r="E22">
-        <v>-3.24</v>
+        <v>-3.007</v>
       </c>
       <c r="F22">
-        <v>4.66</v>
+        <v>4.893000000000001</v>
       </c>
       <c r="G22">
         <v>0.767</v>
@@ -3091,28 +3091,28 @@
         <v>3.467499999999999</v>
       </c>
       <c r="M22">
-        <v>0.234398</v>
+        <v>0.2461179</v>
       </c>
       <c r="N22">
-        <v>3.233101999999999</v>
+        <v>3.221382099999999</v>
       </c>
       <c r="O22">
-        <v>0.4849652999999999</v>
+        <v>0.4832073149999999</v>
       </c>
       <c r="P22">
-        <v>2.748136699999999</v>
+        <v>2.738174784999999</v>
       </c>
       <c r="Q22">
-        <v>3.8681367</v>
+        <v>3.858174784999999</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.1244160087731301</v>
+        <v>0.1252880381018154</v>
       </c>
       <c r="T22">
-        <v>0.9417995276854538</v>
+        <v>0.9522462143425418</v>
       </c>
       <c r="U22">
         <v>0.0503</v>
@@ -3129,7 +3129,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>14.793214959172</v>
+        <v>14.08877615159238</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3137,22 +3137,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.1079561001004342</v>
+        <v>0.1078283931823643</v>
       </c>
       <c r="C23">
-        <v>20.14301343635317</v>
+        <v>19.93627726982519</v>
       </c>
       <c r="D23">
-        <v>24.26901343635317</v>
+        <v>24.29527726982519</v>
       </c>
       <c r="E23">
-        <v>-3.007000000000001</v>
+        <v>-2.774</v>
       </c>
       <c r="F23">
-        <v>4.893</v>
+        <v>5.126</v>
       </c>
       <c r="G23">
         <v>0.767</v>
@@ -3173,28 +3173,28 @@
         <v>3.467499999999999</v>
       </c>
       <c r="M23">
-        <v>0.2461179</v>
+        <v>0.2578378</v>
       </c>
       <c r="N23">
-        <v>3.2213821</v>
+        <v>3.209662199999999</v>
       </c>
       <c r="O23">
-        <v>0.4832073149999999</v>
+        <v>0.4814493299999999</v>
       </c>
       <c r="P23">
-        <v>2.738174785</v>
+        <v>2.72821287</v>
       </c>
       <c r="Q23">
-        <v>3.858174785</v>
+        <v>3.84821287</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.1252880381018154</v>
+        <v>0.1261824271568774</v>
       </c>
       <c r="T23">
-        <v>0.9522462143425415</v>
+        <v>0.9629607647600675</v>
       </c>
       <c r="U23">
         <v>0.0503</v>
@@ -3211,7 +3211,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>14.08877615159239</v>
+        <v>13.44837723561091</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3219,22 +3219,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.1078283931823643</v>
+        <v>0.1079939362642945</v>
       </c>
       <c r="C24">
-        <v>19.93627726982519</v>
+        <v>19.66924306135338</v>
       </c>
       <c r="D24">
-        <v>24.29527726982519</v>
+        <v>24.26124306135339</v>
       </c>
       <c r="E24">
-        <v>-2.774</v>
+        <v>-2.541</v>
       </c>
       <c r="F24">
-        <v>5.126</v>
+        <v>5.359</v>
       </c>
       <c r="G24">
         <v>0.767</v>
@@ -3255,45 +3255,45 @@
         <v>3.467499999999999</v>
       </c>
       <c r="M24">
-        <v>0.2578378</v>
+        <v>0.2775962</v>
       </c>
       <c r="N24">
-        <v>3.209662199999999</v>
+        <v>3.189903799999999</v>
       </c>
       <c r="O24">
-        <v>0.4814493299999999</v>
+        <v>0.4784855699999999</v>
       </c>
       <c r="P24">
-        <v>2.72821287</v>
+        <v>2.71141823</v>
       </c>
       <c r="Q24">
-        <v>3.84821287</v>
+        <v>3.83141823</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.1261824271568774</v>
+        <v>0.1271000470964863</v>
       </c>
       <c r="T24">
-        <v>0.9629607647600675</v>
+        <v>0.9739536151884383</v>
       </c>
       <c r="U24">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V24">
         <v>0.15</v>
       </c>
       <c r="W24">
-        <v>0.04275499999999999</v>
+        <v>0.04403</v>
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y24">
-        <v>13.44837723561091</v>
+        <v>12.4911652248842</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3301,22 +3301,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.1079939362642945</v>
+        <v>0.1078789793462246</v>
       </c>
       <c r="C25">
-        <v>19.66924306135338</v>
+        <v>19.45986707046028</v>
       </c>
       <c r="D25">
-        <v>24.26124306135339</v>
+        <v>24.28486707046028</v>
       </c>
       <c r="E25">
-        <v>-2.541</v>
+        <v>-2.308</v>
       </c>
       <c r="F25">
-        <v>5.359</v>
+        <v>5.592000000000001</v>
       </c>
       <c r="G25">
         <v>0.767</v>
@@ -3337,28 +3337,28 @@
         <v>3.467499999999999</v>
       </c>
       <c r="M25">
-        <v>0.2775962</v>
+        <v>0.2896656</v>
       </c>
       <c r="N25">
-        <v>3.189903799999999</v>
+        <v>3.177834399999999</v>
       </c>
       <c r="O25">
-        <v>0.4784855699999999</v>
+        <v>0.4766751599999999</v>
       </c>
       <c r="P25">
-        <v>2.71141823</v>
+        <v>2.701159239999999</v>
       </c>
       <c r="Q25">
-        <v>3.83141823</v>
+        <v>3.821159239999999</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.1271000470964863</v>
+        <v>0.1280418149292429</v>
       </c>
       <c r="T25">
-        <v>0.9739536151884383</v>
+        <v>0.9852357511543977</v>
       </c>
       <c r="U25">
         <v>0.0518</v>
@@ -3375,7 +3375,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>12.4911652248842</v>
+        <v>11.97070000718069</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3383,22 +3383,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.1078789793462246</v>
+        <v>0.1077640224281548</v>
       </c>
       <c r="C26">
-        <v>19.45986707046028</v>
+        <v>19.25053713143432</v>
       </c>
       <c r="D26">
-        <v>24.28486707046028</v>
+        <v>24.30853713143432</v>
       </c>
       <c r="E26">
-        <v>-2.308000000000001</v>
+        <v>-2.075</v>
       </c>
       <c r="F26">
-        <v>5.592</v>
+        <v>5.825</v>
       </c>
       <c r="G26">
         <v>0.767</v>
@@ -3419,28 +3419,28 @@
         <v>3.467499999999999</v>
       </c>
       <c r="M26">
-        <v>0.2896656</v>
+        <v>0.301735</v>
       </c>
       <c r="N26">
-        <v>3.177834399999999</v>
+        <v>3.165764999999999</v>
       </c>
       <c r="O26">
-        <v>0.4766751599999999</v>
+        <v>0.4748647499999999</v>
       </c>
       <c r="P26">
-        <v>2.701159239999999</v>
+        <v>2.690900249999999</v>
       </c>
       <c r="Q26">
-        <v>3.821159239999999</v>
+        <v>3.81090025</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.1280418149292429</v>
+        <v>0.129008696570873</v>
       </c>
       <c r="T26">
-        <v>0.9852357511543977</v>
+        <v>0.9968187440794494</v>
       </c>
       <c r="U26">
         <v>0.0518</v>
@@ -3457,7 +3457,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>11.97070000718069</v>
+        <v>11.49187200689347</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3465,22 +3465,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.1077640224281548</v>
+        <v>0.1076490655100849</v>
       </c>
       <c r="C27">
-        <v>19.25053713143432</v>
+        <v>19.04125337906487</v>
       </c>
       <c r="D27">
-        <v>24.30853713143432</v>
+        <v>24.33225337906487</v>
       </c>
       <c r="E27">
-        <v>-2.075</v>
+        <v>-1.842</v>
       </c>
       <c r="F27">
-        <v>5.825</v>
+        <v>6.058000000000001</v>
       </c>
       <c r="G27">
         <v>0.767</v>
@@ -3501,28 +3501,28 @@
         <v>3.467499999999999</v>
       </c>
       <c r="M27">
-        <v>0.301735</v>
+        <v>0.3138044</v>
       </c>
       <c r="N27">
-        <v>3.165764999999999</v>
+        <v>3.153695599999999</v>
       </c>
       <c r="O27">
-        <v>0.4748647499999999</v>
+        <v>0.4730543399999999</v>
       </c>
       <c r="P27">
-        <v>2.690900249999999</v>
+        <v>2.680641259999999</v>
       </c>
       <c r="Q27">
-        <v>3.81090025</v>
+        <v>3.800641259999999</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.129008696570873</v>
+        <v>0.1300017101487634</v>
       </c>
       <c r="T27">
-        <v>0.9968187440794494</v>
+        <v>1.00871479086734</v>
       </c>
       <c r="U27">
         <v>0.0518</v>
@@ -3539,7 +3539,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>11.49187200689347</v>
+        <v>11.04987692970525</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3547,22 +3547,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.1076490655100849</v>
+        <v>0.1075341085920151</v>
       </c>
       <c r="C28">
-        <v>19.04125337906487</v>
+        <v>18.83201594866786</v>
       </c>
       <c r="D28">
-        <v>24.33225337906487</v>
+        <v>24.35601594866786</v>
       </c>
       <c r="E28">
-        <v>-1.842</v>
+        <v>-1.609</v>
       </c>
       <c r="F28">
-        <v>6.058000000000001</v>
+        <v>6.291</v>
       </c>
       <c r="G28">
         <v>0.767</v>
@@ -3583,28 +3583,28 @@
         <v>3.467499999999999</v>
       </c>
       <c r="M28">
-        <v>0.3138044</v>
+        <v>0.3258738</v>
       </c>
       <c r="N28">
-        <v>3.153695599999999</v>
+        <v>3.141626199999999</v>
       </c>
       <c r="O28">
-        <v>0.4730543399999999</v>
+        <v>0.4712439299999999</v>
       </c>
       <c r="P28">
-        <v>2.680641259999999</v>
+        <v>2.670382269999999</v>
       </c>
       <c r="Q28">
-        <v>3.800641259999999</v>
+        <v>3.790382269999999</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.1300017101487634</v>
+        <v>0.1310219295781029</v>
       </c>
       <c r="T28">
-        <v>1.00871479086734</v>
+        <v>1.020936756745311</v>
       </c>
       <c r="U28">
         <v>0.0518</v>
@@ -3621,7 +3621,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>11.04987692970525</v>
+        <v>10.64062222860506</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3629,22 +3629,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.1075341085920151</v>
+        <v>0.1074191516739452</v>
       </c>
       <c r="C29">
-        <v>18.83201594866786</v>
+        <v>18.62282497608828</v>
       </c>
       <c r="D29">
-        <v>24.35601594866786</v>
+        <v>24.37982497608828</v>
       </c>
       <c r="E29">
-        <v>-1.609</v>
+        <v>-1.375999999999999</v>
       </c>
       <c r="F29">
-        <v>6.291</v>
+        <v>6.524000000000001</v>
       </c>
       <c r="G29">
         <v>0.767</v>
@@ -3665,28 +3665,28 @@
         <v>3.467499999999999</v>
       </c>
       <c r="M29">
-        <v>0.3258738</v>
+        <v>0.3379432000000001</v>
       </c>
       <c r="N29">
-        <v>3.141626199999999</v>
+        <v>3.129556799999999</v>
       </c>
       <c r="O29">
-        <v>0.4712439299999999</v>
+        <v>0.4694335199999998</v>
       </c>
       <c r="P29">
-        <v>2.670382269999999</v>
+        <v>2.660123279999999</v>
       </c>
       <c r="Q29">
-        <v>3.790382269999999</v>
+        <v>3.780123279999999</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.1310219295781029</v>
+        <v>0.1320704884360351</v>
       </c>
       <c r="T29">
-        <v>1.020936756745311</v>
+        <v>1.033498221675447</v>
       </c>
       <c r="U29">
         <v>0.0518</v>
@@ -3703,7 +3703,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>10.64062222860506</v>
+        <v>10.26060000615488</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3711,22 +3711,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.1074191516739452</v>
+        <v>0.1073041947558754</v>
       </c>
       <c r="C30">
-        <v>18.62282497608828</v>
+        <v>18.41368059770286</v>
       </c>
       <c r="D30">
-        <v>24.37982497608828</v>
+        <v>24.40368059770286</v>
       </c>
       <c r="E30">
-        <v>-1.375999999999999</v>
+        <v>-1.142999999999999</v>
       </c>
       <c r="F30">
-        <v>6.524000000000001</v>
+        <v>6.757000000000001</v>
       </c>
       <c r="G30">
         <v>0.767</v>
@@ -3747,28 +3747,28 @@
         <v>3.467499999999999</v>
       </c>
       <c r="M30">
-        <v>0.3379432000000001</v>
+        <v>0.3500126000000001</v>
       </c>
       <c r="N30">
-        <v>3.129556799999999</v>
+        <v>3.117487399999999</v>
       </c>
       <c r="O30">
-        <v>0.4694335199999998</v>
+        <v>0.4676231099999999</v>
       </c>
       <c r="P30">
-        <v>2.660123279999999</v>
+        <v>2.64986429</v>
       </c>
       <c r="Q30">
-        <v>3.780123279999999</v>
+        <v>3.76986429</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.1320704884360351</v>
+        <v>0.1331485841632047</v>
       </c>
       <c r="T30">
-        <v>1.033498221675447</v>
+        <v>1.046413530688121</v>
       </c>
       <c r="U30">
         <v>0.0518</v>
@@ -3785,7 +3785,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>10.26060000615488</v>
+        <v>9.906786212839192</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3793,22 +3793,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.1073041947558754</v>
+        <v>0.1076227378378055</v>
       </c>
       <c r="C31">
-        <v>18.41368059770286</v>
+        <v>18.11469143767614</v>
       </c>
       <c r="D31">
-        <v>24.40368059770286</v>
+        <v>24.33769143767614</v>
       </c>
       <c r="E31">
-        <v>-1.143000000000001</v>
+        <v>-0.9100000000000001</v>
       </c>
       <c r="F31">
-        <v>6.757</v>
+        <v>6.99</v>
       </c>
       <c r="G31">
         <v>0.767</v>
@@ -3829,45 +3829,45 @@
         <v>3.467499999999999</v>
       </c>
       <c r="M31">
-        <v>0.3500126</v>
+        <v>0.373965</v>
       </c>
       <c r="N31">
-        <v>3.117487399999999</v>
+        <v>3.093534999999999</v>
       </c>
       <c r="O31">
-        <v>0.4676231099999999</v>
+        <v>0.4640302499999999</v>
       </c>
       <c r="P31">
-        <v>2.64986429</v>
+        <v>2.629504749999999</v>
       </c>
       <c r="Q31">
-        <v>3.76986429</v>
+        <v>3.749504749999999</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.1331485841632047</v>
+        <v>0.1342574826254365</v>
       </c>
       <c r="T31">
-        <v>1.046413530688121</v>
+        <v>1.05969784852973</v>
       </c>
       <c r="U31">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V31">
         <v>0.15</v>
       </c>
       <c r="W31">
-        <v>0.04403</v>
+        <v>0.04547499999999999</v>
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y31">
-        <v>9.906786212839195</v>
+        <v>9.272258099019959</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3875,22 +3875,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.1076227378378055</v>
+        <v>0.1075222309197357</v>
       </c>
       <c r="C32">
-        <v>18.11469143767614</v>
+        <v>17.9024738099701</v>
       </c>
       <c r="D32">
-        <v>24.33769143767614</v>
+        <v>24.3584738099701</v>
       </c>
       <c r="E32">
-        <v>-0.9100000000000001</v>
+        <v>-0.6770000000000005</v>
       </c>
       <c r="F32">
-        <v>6.99</v>
+        <v>7.223</v>
       </c>
       <c r="G32">
         <v>0.767</v>
@@ -3911,28 +3911,28 @@
         <v>3.467499999999999</v>
       </c>
       <c r="M32">
-        <v>0.373965</v>
+        <v>0.3864305</v>
       </c>
       <c r="N32">
-        <v>3.093534999999999</v>
+        <v>3.081069499999999</v>
       </c>
       <c r="O32">
-        <v>0.4640302499999999</v>
+        <v>0.4621604249999999</v>
       </c>
       <c r="P32">
-        <v>2.629504749999999</v>
+        <v>2.618909074999999</v>
       </c>
       <c r="Q32">
-        <v>3.749504749999999</v>
+        <v>3.738909075</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1342574826254365</v>
+        <v>0.1353985230720807</v>
       </c>
       <c r="T32">
-        <v>1.05969784852973</v>
+        <v>1.0733672190624</v>
       </c>
       <c r="U32">
         <v>0.0535</v>
@@ -3949,7 +3949,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>9.272258099019959</v>
+        <v>8.973152999051575</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3957,22 +3957,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.1075222309197357</v>
+        <v>0.1074217240016658</v>
       </c>
       <c r="C33">
-        <v>17.9024738099701</v>
+        <v>17.69029170544647</v>
       </c>
       <c r="D33">
-        <v>24.3584738099701</v>
+        <v>24.37929170544647</v>
       </c>
       <c r="E33">
-        <v>-0.6770000000000005</v>
+        <v>-0.444</v>
       </c>
       <c r="F33">
-        <v>7.223</v>
+        <v>7.456</v>
       </c>
       <c r="G33">
         <v>0.767</v>
@@ -3993,28 +3993,28 @@
         <v>3.467499999999999</v>
       </c>
       <c r="M33">
-        <v>0.3864305</v>
+        <v>0.398896</v>
       </c>
       <c r="N33">
-        <v>3.081069499999999</v>
+        <v>3.068603999999999</v>
       </c>
       <c r="O33">
-        <v>0.4621604249999999</v>
+        <v>0.4602905999999999</v>
       </c>
       <c r="P33">
-        <v>2.618909074999999</v>
+        <v>2.608313399999999</v>
       </c>
       <c r="Q33">
-        <v>3.738909075</v>
+        <v>3.728313399999999</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.1353985230720807</v>
+        <v>0.1365731235318615</v>
       </c>
       <c r="T33">
-        <v>1.0733672190624</v>
+        <v>1.087438629904854</v>
       </c>
       <c r="U33">
         <v>0.0535</v>
@@ -4031,7 +4031,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>8.973152999051575</v>
+        <v>8.692741967831211</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4039,22 +4039,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.1074217240016658</v>
+        <v>0.107321217083596</v>
       </c>
       <c r="C34">
-        <v>17.69029170544647</v>
+        <v>17.47814521526249</v>
       </c>
       <c r="D34">
-        <v>24.37929170544647</v>
+        <v>24.40014521526249</v>
       </c>
       <c r="E34">
-        <v>-0.444</v>
+        <v>-0.2109999999999994</v>
       </c>
       <c r="F34">
-        <v>7.456</v>
+        <v>7.689000000000001</v>
       </c>
       <c r="G34">
         <v>0.767</v>
@@ -4075,28 +4075,28 @@
         <v>3.467499999999999</v>
       </c>
       <c r="M34">
-        <v>0.398896</v>
+        <v>0.4113615</v>
       </c>
       <c r="N34">
-        <v>3.068603999999999</v>
+        <v>3.056138499999999</v>
       </c>
       <c r="O34">
-        <v>0.4602905999999999</v>
+        <v>0.4584207749999999</v>
       </c>
       <c r="P34">
-        <v>2.608313399999999</v>
+        <v>2.597717724999999</v>
       </c>
       <c r="Q34">
-        <v>3.728313399999999</v>
+        <v>3.717717725</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1365731235318615</v>
+        <v>0.1377827866919343</v>
       </c>
       <c r="T34">
-        <v>1.087438629904854</v>
+        <v>1.101930082862008</v>
       </c>
       <c r="U34">
         <v>0.0535</v>
@@ -4113,7 +4113,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>8.692741967831211</v>
+        <v>8.4293255445636</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4121,22 +4121,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.107321217083596</v>
+        <v>0.1072207101655261</v>
       </c>
       <c r="C35">
-        <v>17.47814521526249</v>
+        <v>17.26603443088757</v>
       </c>
       <c r="D35">
-        <v>24.40014521526249</v>
+        <v>24.42103443088757</v>
       </c>
       <c r="E35">
-        <v>-0.2109999999999994</v>
+        <v>0.02200000000000024</v>
       </c>
       <c r="F35">
-        <v>7.689000000000001</v>
+        <v>7.922000000000001</v>
       </c>
       <c r="G35">
         <v>0.767</v>
@@ -4157,28 +4157,28 @@
         <v>3.467499999999999</v>
       </c>
       <c r="M35">
-        <v>0.4113615</v>
+        <v>0.423827</v>
       </c>
       <c r="N35">
-        <v>3.056138499999999</v>
+        <v>3.043672999999999</v>
       </c>
       <c r="O35">
-        <v>0.4584207749999999</v>
+        <v>0.4565509499999998</v>
       </c>
       <c r="P35">
-        <v>2.597717724999999</v>
+        <v>2.587122049999999</v>
       </c>
       <c r="Q35">
-        <v>3.717717725</v>
+        <v>3.707122049999999</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1377827866919343</v>
+        <v>0.1390291063114032</v>
       </c>
       <c r="T35">
-        <v>1.101930082862008</v>
+        <v>1.116860670757258</v>
       </c>
       <c r="U35">
         <v>0.0535</v>
@@ -4195,7 +4195,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>8.4293255445636</v>
+        <v>8.181404205017611</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4203,22 +4203,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.1072207101655261</v>
+        <v>0.1071202032474562</v>
       </c>
       <c r="C36">
-        <v>17.26603443088757</v>
+        <v>17.05395944410462</v>
       </c>
       <c r="D36">
-        <v>24.42103443088757</v>
+        <v>24.44195944410463</v>
       </c>
       <c r="E36">
-        <v>0.02200000000000024</v>
+        <v>0.2550000000000008</v>
       </c>
       <c r="F36">
-        <v>7.922000000000001</v>
+        <v>8.155000000000001</v>
       </c>
       <c r="G36">
         <v>0.767</v>
@@ -4239,28 +4239,28 @@
         <v>3.467499999999999</v>
       </c>
       <c r="M36">
-        <v>0.423827</v>
+        <v>0.4362925</v>
       </c>
       <c r="N36">
-        <v>3.043672999999999</v>
+        <v>3.031207499999999</v>
       </c>
       <c r="O36">
-        <v>0.4565509499999998</v>
+        <v>0.4546811249999999</v>
       </c>
       <c r="P36">
-        <v>2.587122049999999</v>
+        <v>2.576526374999999</v>
       </c>
       <c r="Q36">
-        <v>3.707122049999999</v>
+        <v>3.696526374999999</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1390291063114032</v>
+        <v>0.1403137742268558</v>
       </c>
       <c r="T36">
-        <v>1.116860670757258</v>
+        <v>1.132250661356977</v>
       </c>
       <c r="U36">
         <v>0.0535</v>
@@ -4277,7 +4277,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>8.181404205017611</v>
+        <v>7.947649799159965</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4285,22 +4285,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.1071202032474562</v>
+        <v>0.1070196963293864</v>
       </c>
       <c r="C37">
-        <v>17.05395944410462</v>
+        <v>16.8419203470114</v>
       </c>
       <c r="D37">
-        <v>24.44195944410463</v>
+        <v>24.4629203470114</v>
       </c>
       <c r="E37">
-        <v>0.2550000000000008</v>
+        <v>0.4880000000000013</v>
       </c>
       <c r="F37">
-        <v>8.155000000000001</v>
+        <v>8.388000000000002</v>
       </c>
       <c r="G37">
         <v>0.767</v>
@@ -4321,28 +4321,28 @@
         <v>3.467499999999999</v>
       </c>
       <c r="M37">
-        <v>0.4362925</v>
+        <v>0.4487580000000001</v>
       </c>
       <c r="N37">
-        <v>3.031207499999999</v>
+        <v>3.018741999999999</v>
       </c>
       <c r="O37">
-        <v>0.4546811249999999</v>
+        <v>0.4528112999999999</v>
       </c>
       <c r="P37">
-        <v>2.576526374999999</v>
+        <v>2.565930699999999</v>
       </c>
       <c r="Q37">
-        <v>3.696526374999999</v>
+        <v>3.685930699999999</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1403137742268558</v>
+        <v>0.1416385880146663</v>
       </c>
       <c r="T37">
-        <v>1.132250661356977</v>
+        <v>1.148121589162937</v>
       </c>
       <c r="U37">
         <v>0.0535</v>
@@ -4359,7 +4359,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>7.947649799159965</v>
+        <v>7.726881749183298</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4367,22 +4367,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.1070196963293864</v>
+        <v>0.1071707894113166</v>
       </c>
       <c r="C38">
-        <v>16.8419203470114</v>
+        <v>16.57742318985775</v>
       </c>
       <c r="D38">
-        <v>24.4629203470114</v>
+        <v>24.43142318985775</v>
       </c>
       <c r="E38">
-        <v>0.4879999999999995</v>
+        <v>0.7210000000000001</v>
       </c>
       <c r="F38">
-        <v>8.388</v>
+        <v>8.621</v>
       </c>
       <c r="G38">
         <v>0.767</v>
@@ -4403,45 +4403,45 @@
         <v>3.467499999999999</v>
       </c>
       <c r="M38">
-        <v>0.448758</v>
+        <v>0.4681203</v>
       </c>
       <c r="N38">
-        <v>3.018742</v>
+        <v>2.9993797</v>
       </c>
       <c r="O38">
-        <v>0.4528112999999999</v>
+        <v>0.4499069549999999</v>
       </c>
       <c r="P38">
-        <v>2.5659307</v>
+        <v>2.549472745</v>
       </c>
       <c r="Q38">
-        <v>3.6859307</v>
+        <v>3.669472745</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1416385880146663</v>
+        <v>0.1430054593830422</v>
       </c>
       <c r="T38">
-        <v>1.148121589162937</v>
+        <v>1.164496355946865</v>
       </c>
       <c r="U38">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V38">
         <v>0.15</v>
       </c>
       <c r="W38">
-        <v>0.04547499999999999</v>
+        <v>0.046155</v>
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y38">
-        <v>7.726881749183301</v>
+        <v>7.407283982343853</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4449,22 +4449,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.1071707894113166</v>
+        <v>0.1070770824932467</v>
       </c>
       <c r="C39">
-        <v>16.57742318985775</v>
+        <v>16.36394795560852</v>
       </c>
       <c r="D39">
-        <v>24.43142318985775</v>
+        <v>24.45094795560852</v>
       </c>
       <c r="E39">
-        <v>0.7210000000000001</v>
+        <v>0.9540000000000006</v>
       </c>
       <c r="F39">
-        <v>8.621</v>
+        <v>8.854000000000001</v>
       </c>
       <c r="G39">
         <v>0.767</v>
@@ -4485,28 +4485,28 @@
         <v>3.467499999999999</v>
       </c>
       <c r="M39">
-        <v>0.4681203</v>
+        <v>0.4807722</v>
       </c>
       <c r="N39">
-        <v>2.9993797</v>
+        <v>2.986727799999999</v>
       </c>
       <c r="O39">
-        <v>0.4499069549999999</v>
+        <v>0.4480091699999999</v>
       </c>
       <c r="P39">
-        <v>2.549472745</v>
+        <v>2.53871863</v>
       </c>
       <c r="Q39">
-        <v>3.669472745</v>
+        <v>3.65871863</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1430054593830422</v>
+        <v>0.1444164233762044</v>
       </c>
       <c r="T39">
-        <v>1.164496355946865</v>
+        <v>1.181399341014144</v>
       </c>
       <c r="U39">
         <v>0.0543</v>
@@ -4523,7 +4523,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>7.407283982343853</v>
+        <v>7.212355456492698</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4531,22 +4531,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.1070770824932467</v>
+        <v>0.1069833755751768</v>
       </c>
       <c r="C40">
-        <v>16.36394795560852</v>
+        <v>16.15050395338154</v>
       </c>
       <c r="D40">
-        <v>24.45094795560852</v>
+        <v>24.47050395338155</v>
       </c>
       <c r="E40">
-        <v>0.9540000000000006</v>
+        <v>1.186999999999999</v>
       </c>
       <c r="F40">
-        <v>8.854000000000001</v>
+        <v>9.087</v>
       </c>
       <c r="G40">
         <v>0.767</v>
@@ -4567,28 +4567,28 @@
         <v>3.467499999999999</v>
       </c>
       <c r="M40">
-        <v>0.4807722</v>
+        <v>0.4934241</v>
       </c>
       <c r="N40">
-        <v>2.986727799999999</v>
+        <v>2.974075899999999</v>
       </c>
       <c r="O40">
-        <v>0.4480091699999999</v>
+        <v>0.4461113849999999</v>
       </c>
       <c r="P40">
-        <v>2.53871863</v>
+        <v>2.527964514999999</v>
       </c>
       <c r="Q40">
-        <v>3.65871863</v>
+        <v>3.647964515</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1444164233762044</v>
+        <v>0.1458736484838965</v>
       </c>
       <c r="T40">
-        <v>1.181399341014144</v>
+        <v>1.198856522313138</v>
       </c>
       <c r="U40">
         <v>0.0543</v>
@@ -4605,7 +4605,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>7.212355456492698</v>
+        <v>7.027423265300579</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4613,22 +4613,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.1069833755751768</v>
+        <v>0.106889668657107</v>
       </c>
       <c r="C41">
-        <v>16.15050395338154</v>
+        <v>15.93709125817544</v>
       </c>
       <c r="D41">
-        <v>24.47050395338155</v>
+        <v>24.49009125817544</v>
       </c>
       <c r="E41">
-        <v>1.186999999999999</v>
+        <v>1.42</v>
       </c>
       <c r="F41">
-        <v>9.087</v>
+        <v>9.32</v>
       </c>
       <c r="G41">
         <v>0.767</v>
@@ -4649,28 +4649,28 @@
         <v>3.467499999999999</v>
       </c>
       <c r="M41">
-        <v>0.4934241</v>
+        <v>0.506076</v>
       </c>
       <c r="N41">
-        <v>2.974075899999999</v>
+        <v>2.961423999999999</v>
       </c>
       <c r="O41">
-        <v>0.4461113849999999</v>
+        <v>0.4442135999999999</v>
       </c>
       <c r="P41">
-        <v>2.527964514999999</v>
+        <v>2.517210399999999</v>
       </c>
       <c r="Q41">
-        <v>3.647964515</v>
+        <v>3.637210399999999</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1458736484838965</v>
+        <v>0.147379447761845</v>
       </c>
       <c r="T41">
-        <v>1.198856522313138</v>
+        <v>1.216895609655432</v>
       </c>
       <c r="U41">
         <v>0.0543</v>
@@ -4687,7 +4687,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>7.027423265300579</v>
+        <v>6.851737683668064</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4695,22 +4695,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.106889668657107</v>
+        <v>0.1067959617390371</v>
       </c>
       <c r="C42">
-        <v>15.93709125817544</v>
+        <v>15.72370994522912</v>
       </c>
       <c r="D42">
-        <v>24.49009125817544</v>
+        <v>24.50970994522912</v>
       </c>
       <c r="E42">
-        <v>1.42</v>
+        <v>1.653</v>
       </c>
       <c r="F42">
-        <v>9.32</v>
+        <v>9.553000000000001</v>
       </c>
       <c r="G42">
         <v>0.767</v>
@@ -4731,28 +4731,28 @@
         <v>3.467499999999999</v>
       </c>
       <c r="M42">
-        <v>0.506076</v>
+        <v>0.5187279</v>
       </c>
       <c r="N42">
-        <v>2.961423999999999</v>
+        <v>2.948772099999999</v>
       </c>
       <c r="O42">
-        <v>0.4442135999999999</v>
+        <v>0.4423158149999999</v>
       </c>
       <c r="P42">
-        <v>2.517210399999999</v>
+        <v>2.506456285</v>
       </c>
       <c r="Q42">
-        <v>3.637210399999999</v>
+        <v>3.626456285</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.147379447761845</v>
+        <v>0.1489362910831138</v>
       </c>
       <c r="T42">
-        <v>1.216895609655432</v>
+        <v>1.235546191483905</v>
       </c>
       <c r="U42">
         <v>0.0543</v>
@@ -4769,7 +4769,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>6.851737683668064</v>
+        <v>6.684622130407868</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4777,22 +4777,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.1067959617390371</v>
+        <v>0.1067022548209673</v>
       </c>
       <c r="C43">
-        <v>15.72370994522912</v>
+        <v>15.51036009002278</v>
       </c>
       <c r="D43">
-        <v>24.50970994522912</v>
+        <v>24.52936009002278</v>
       </c>
       <c r="E43">
-        <v>1.653</v>
+        <v>1.886000000000001</v>
       </c>
       <c r="F43">
-        <v>9.553000000000001</v>
+        <v>9.786000000000001</v>
       </c>
       <c r="G43">
         <v>0.767</v>
@@ -4813,28 +4813,28 @@
         <v>3.467499999999999</v>
       </c>
       <c r="M43">
-        <v>0.5187279</v>
+        <v>0.5313798000000001</v>
       </c>
       <c r="N43">
-        <v>2.948772099999999</v>
+        <v>2.9361202</v>
       </c>
       <c r="O43">
-        <v>0.4423158149999999</v>
+        <v>0.4404180299999999</v>
       </c>
       <c r="P43">
-        <v>2.506456285</v>
+        <v>2.495702169999999</v>
       </c>
       <c r="Q43">
-        <v>3.626456285</v>
+        <v>3.61570217</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1489362910831138</v>
+        <v>0.1505468186568402</v>
       </c>
       <c r="T43">
-        <v>1.235546191483905</v>
+        <v>1.254839896823705</v>
       </c>
       <c r="U43">
         <v>0.0543</v>
@@ -4851,7 +4851,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>6.684622130407868</v>
+        <v>6.525464460636251</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4859,22 +4859,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.1067022548209673</v>
+        <v>0.1066085479028974</v>
       </c>
       <c r="C44">
-        <v>15.51036009002278</v>
+        <v>15.29704176827888</v>
       </c>
       <c r="D44">
-        <v>24.52936009002278</v>
+        <v>24.54904176827888</v>
       </c>
       <c r="E44">
-        <v>1.885999999999999</v>
+        <v>2.119</v>
       </c>
       <c r="F44">
-        <v>9.786</v>
+        <v>10.019</v>
       </c>
       <c r="G44">
         <v>0.767</v>
@@ -4895,28 +4895,28 @@
         <v>3.467499999999999</v>
       </c>
       <c r="M44">
-        <v>0.5313798</v>
+        <v>0.5440317</v>
       </c>
       <c r="N44">
-        <v>2.9361202</v>
+        <v>2.923468299999999</v>
       </c>
       <c r="O44">
-        <v>0.4404180299999999</v>
+        <v>0.4385202449999999</v>
       </c>
       <c r="P44">
-        <v>2.495702169999999</v>
+        <v>2.484948054999999</v>
       </c>
       <c r="Q44">
-        <v>3.61570217</v>
+        <v>3.604948054999999</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1505468186568402</v>
+        <v>0.1522138559699955</v>
       </c>
       <c r="T44">
-        <v>1.254839896823704</v>
+        <v>1.27481057428069</v>
       </c>
       <c r="U44">
         <v>0.0543</v>
@@ -4933,7 +4933,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>6.525464460636252</v>
+        <v>6.373709473179595</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4941,22 +4941,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.1066085479028974</v>
+        <v>0.1065148409848276</v>
       </c>
       <c r="C45">
-        <v>15.29704176827888</v>
+        <v>15.08375505596309</v>
       </c>
       <c r="D45">
-        <v>24.54904176827888</v>
+        <v>24.56875505596309</v>
       </c>
       <c r="E45">
-        <v>2.119</v>
+        <v>2.352</v>
       </c>
       <c r="F45">
-        <v>10.019</v>
+        <v>10.252</v>
       </c>
       <c r="G45">
         <v>0.767</v>
@@ -4977,28 +4977,28 @@
         <v>3.467499999999999</v>
       </c>
       <c r="M45">
-        <v>0.5440317</v>
+        <v>0.5566836000000001</v>
       </c>
       <c r="N45">
-        <v>2.923468299999999</v>
+        <v>2.910816399999999</v>
       </c>
       <c r="O45">
-        <v>0.4385202449999999</v>
+        <v>0.4366224599999999</v>
       </c>
       <c r="P45">
-        <v>2.484948054999999</v>
+        <v>2.47419394</v>
       </c>
       <c r="Q45">
-        <v>3.604948054999999</v>
+        <v>3.59419394</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1522138559699955</v>
+        <v>0.1539404303300493</v>
       </c>
       <c r="T45">
-        <v>1.27481057428069</v>
+        <v>1.295494490218283</v>
       </c>
       <c r="U45">
         <v>0.0543</v>
@@ -5015,7 +5015,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>6.373709473179595</v>
+        <v>6.22885243969824</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5023,22 +5023,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.1065148409848276</v>
+        <v>0.1068036340667577</v>
       </c>
       <c r="C46">
-        <v>15.08375505596309</v>
+        <v>14.79010246842671</v>
       </c>
       <c r="D46">
-        <v>24.56875505596309</v>
+        <v>24.50810246842671</v>
       </c>
       <c r="E46">
-        <v>2.352</v>
+        <v>2.585000000000001</v>
       </c>
       <c r="F46">
-        <v>10.252</v>
+        <v>10.485</v>
       </c>
       <c r="G46">
         <v>0.767</v>
@@ -5059,45 +5059,45 @@
         <v>3.467499999999999</v>
       </c>
       <c r="M46">
-        <v>0.5566836000000001</v>
+        <v>0.5798205000000001</v>
       </c>
       <c r="N46">
-        <v>2.910816399999999</v>
+        <v>2.887679499999999</v>
       </c>
       <c r="O46">
-        <v>0.4366224599999999</v>
+        <v>0.4331519249999998</v>
       </c>
       <c r="P46">
-        <v>2.47419394</v>
+        <v>2.454527574999999</v>
       </c>
       <c r="Q46">
-        <v>3.59419394</v>
+        <v>3.574527574999999</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1539404303300493</v>
+        <v>0.1557297892122868</v>
       </c>
       <c r="T46">
-        <v>1.295494490218283</v>
+        <v>1.316930548553606</v>
       </c>
       <c r="U46">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V46">
         <v>0.15</v>
       </c>
       <c r="W46">
-        <v>0.046155</v>
+        <v>0.047005</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y46">
-        <v>6.22885243969824</v>
+        <v>5.980299075317273</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5105,22 +5105,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.1068036340667577</v>
+        <v>0.1067184271486879</v>
       </c>
       <c r="C47">
-        <v>14.79010246842671</v>
+        <v>14.57496653735858</v>
       </c>
       <c r="D47">
-        <v>24.50810246842671</v>
+        <v>24.52596653735858</v>
       </c>
       <c r="E47">
-        <v>2.585000000000001</v>
+        <v>2.818</v>
       </c>
       <c r="F47">
-        <v>10.485</v>
+        <v>10.718</v>
       </c>
       <c r="G47">
         <v>0.767</v>
@@ -5141,28 +5141,28 @@
         <v>3.467499999999999</v>
       </c>
       <c r="M47">
-        <v>0.5798205000000001</v>
+        <v>0.5927054</v>
       </c>
       <c r="N47">
-        <v>2.887679499999999</v>
+        <v>2.8747946</v>
       </c>
       <c r="O47">
-        <v>0.4331519249999998</v>
+        <v>0.4312191899999999</v>
       </c>
       <c r="P47">
-        <v>2.454527574999999</v>
+        <v>2.44357541</v>
       </c>
       <c r="Q47">
-        <v>3.574527574999999</v>
+        <v>3.56357541</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1557297892122868</v>
+        <v>0.1575854206457183</v>
       </c>
       <c r="T47">
-        <v>1.316930548553606</v>
+        <v>1.339160534975422</v>
       </c>
       <c r="U47">
         <v>0.0553</v>
@@ -5179,7 +5179,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>5.980299075317273</v>
+        <v>5.850292573679941</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5187,22 +5187,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.1067184271486879</v>
+        <v>0.1066332202306181</v>
       </c>
       <c r="C48">
-        <v>14.57496653735858</v>
+        <v>14.3598566676912</v>
       </c>
       <c r="D48">
-        <v>24.52596653735858</v>
+        <v>24.54385666769121</v>
       </c>
       <c r="E48">
-        <v>2.818</v>
+        <v>3.051</v>
       </c>
       <c r="F48">
-        <v>10.718</v>
+        <v>10.951</v>
       </c>
       <c r="G48">
         <v>0.767</v>
@@ -5223,28 +5223,28 @@
         <v>3.467499999999999</v>
       </c>
       <c r="M48">
-        <v>0.5927054</v>
+        <v>0.6055903</v>
       </c>
       <c r="N48">
-        <v>2.8747946</v>
+        <v>2.861909699999999</v>
       </c>
       <c r="O48">
-        <v>0.4312191899999999</v>
+        <v>0.4292864549999998</v>
       </c>
       <c r="P48">
-        <v>2.44357541</v>
+        <v>2.432623244999999</v>
       </c>
       <c r="Q48">
-        <v>3.56357541</v>
+        <v>3.552623244999999</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1575854206457183</v>
+        <v>0.1595110759068265</v>
       </c>
       <c r="T48">
-        <v>1.339160534975422</v>
+        <v>1.362229388809382</v>
       </c>
       <c r="U48">
         <v>0.0553</v>
@@ -5261,7 +5261,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>5.850292573679941</v>
+        <v>5.725818263601645</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5269,22 +5269,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.1066332202306181</v>
+        <v>0.1065480133125482</v>
       </c>
       <c r="C49">
-        <v>14.3598566676912</v>
+        <v>14.14477291649662</v>
       </c>
       <c r="D49">
-        <v>24.54385666769121</v>
+        <v>24.56177291649662</v>
       </c>
       <c r="E49">
-        <v>3.051</v>
+        <v>3.284000000000001</v>
       </c>
       <c r="F49">
-        <v>10.951</v>
+        <v>11.184</v>
       </c>
       <c r="G49">
         <v>0.767</v>
@@ -5305,28 +5305,28 @@
         <v>3.467499999999999</v>
       </c>
       <c r="M49">
-        <v>0.6055903</v>
+        <v>0.6184752000000001</v>
       </c>
       <c r="N49">
-        <v>2.861909699999999</v>
+        <v>2.849024799999999</v>
       </c>
       <c r="O49">
-        <v>0.4292864549999998</v>
+        <v>0.4273537199999999</v>
       </c>
       <c r="P49">
-        <v>2.432623244999999</v>
+        <v>2.421671079999999</v>
       </c>
       <c r="Q49">
-        <v>3.552623244999999</v>
+        <v>3.54167108</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1595110759068265</v>
+        <v>0.1615107948318234</v>
       </c>
       <c r="T49">
-        <v>1.362229388809382</v>
+        <v>1.386185506252341</v>
       </c>
       <c r="U49">
         <v>0.0553</v>
@@ -5343,7 +5343,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>5.725818263601645</v>
+        <v>5.606530383109943</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5351,22 +5351,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.1065480133125482</v>
+        <v>0.1064628063944783</v>
       </c>
       <c r="C50">
-        <v>14.14477291649662</v>
+        <v>13.92971534101361</v>
       </c>
       <c r="D50">
-        <v>24.56177291649662</v>
+        <v>24.57971534101361</v>
       </c>
       <c r="E50">
-        <v>3.283999999999999</v>
+        <v>3.516999999999999</v>
       </c>
       <c r="F50">
-        <v>11.184</v>
+        <v>11.417</v>
       </c>
       <c r="G50">
         <v>0.767</v>
@@ -5387,28 +5387,28 @@
         <v>3.467499999999999</v>
       </c>
       <c r="M50">
-        <v>0.6184752</v>
+        <v>0.6313601</v>
       </c>
       <c r="N50">
-        <v>2.8490248</v>
+        <v>2.836139899999999</v>
       </c>
       <c r="O50">
-        <v>0.4273537199999999</v>
+        <v>0.4254209849999999</v>
       </c>
       <c r="P50">
-        <v>2.421671079999999</v>
+        <v>2.410718914999999</v>
       </c>
       <c r="Q50">
-        <v>3.54167108</v>
+        <v>3.530718915</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1615107948318234</v>
+        <v>0.1635889341068203</v>
       </c>
       <c r="T50">
-        <v>1.386185506252341</v>
+        <v>1.411081079281298</v>
       </c>
       <c r="U50">
         <v>0.0553</v>
@@ -5425,7 +5425,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>5.606530383109945</v>
+        <v>5.492111395699537</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5433,22 +5433,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.1064628063944783</v>
+        <v>0.1063775994764085</v>
       </c>
       <c r="C51">
-        <v>13.92971534101361</v>
+        <v>13.71468399864833</v>
       </c>
       <c r="D51">
-        <v>24.57971534101361</v>
+        <v>24.59768399864833</v>
       </c>
       <c r="E51">
-        <v>3.516999999999999</v>
+        <v>3.75</v>
       </c>
       <c r="F51">
-        <v>11.417</v>
+        <v>11.65</v>
       </c>
       <c r="G51">
         <v>0.767</v>
@@ -5469,28 +5469,28 @@
         <v>3.467499999999999</v>
       </c>
       <c r="M51">
-        <v>0.6313601</v>
+        <v>0.6442450000000001</v>
       </c>
       <c r="N51">
-        <v>2.836139899999999</v>
+        <v>2.823254999999999</v>
       </c>
       <c r="O51">
-        <v>0.4254209849999999</v>
+        <v>0.4234882499999998</v>
       </c>
       <c r="P51">
-        <v>2.410718914999999</v>
+        <v>2.39976675</v>
       </c>
       <c r="Q51">
-        <v>3.530718915</v>
+        <v>3.51976675</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1635889341068203</v>
+        <v>0.165750198952817</v>
       </c>
       <c r="T51">
-        <v>1.411081079281298</v>
+        <v>1.436972475231414</v>
       </c>
       <c r="U51">
         <v>0.0553</v>
@@ -5507,7 +5507,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>5.492111395699537</v>
+        <v>5.382269167785545</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5515,22 +5515,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.1063775994764085</v>
+        <v>0.1062923925583386</v>
       </c>
       <c r="C52">
-        <v>13.71468399864833</v>
+        <v>13.49967894697495</v>
       </c>
       <c r="D52">
-        <v>24.59768399864833</v>
+        <v>24.61567894697495</v>
       </c>
       <c r="E52">
-        <v>3.75</v>
+        <v>3.983000000000001</v>
       </c>
       <c r="F52">
-        <v>11.65</v>
+        <v>11.883</v>
       </c>
       <c r="G52">
         <v>0.767</v>
@@ -5551,28 +5551,28 @@
         <v>3.467499999999999</v>
       </c>
       <c r="M52">
-        <v>0.6442450000000001</v>
+        <v>0.6571299</v>
       </c>
       <c r="N52">
-        <v>2.823254999999999</v>
+        <v>2.810370099999999</v>
       </c>
       <c r="O52">
-        <v>0.4234882499999998</v>
+        <v>0.4215555149999999</v>
       </c>
       <c r="P52">
-        <v>2.39976675</v>
+        <v>2.388814585</v>
       </c>
       <c r="Q52">
-        <v>3.51976675</v>
+        <v>3.508814585</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.165750198952817</v>
+        <v>0.167999678690487</v>
       </c>
       <c r="T52">
-        <v>1.436972475231414</v>
+        <v>1.463920662852963</v>
       </c>
       <c r="U52">
         <v>0.0553</v>
@@ -5589,7 +5589,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>5.382269167785545</v>
+        <v>5.276734478221123</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5597,22 +5597,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.1062923925583386</v>
+        <v>0.1062071856402688</v>
       </c>
       <c r="C53">
-        <v>13.49967894697495</v>
+        <v>13.28470024373622</v>
       </c>
       <c r="D53">
-        <v>24.61567894697495</v>
+        <v>24.63370024373622</v>
       </c>
       <c r="E53">
-        <v>3.983000000000001</v>
+        <v>4.216000000000001</v>
       </c>
       <c r="F53">
-        <v>11.883</v>
+        <v>12.116</v>
       </c>
       <c r="G53">
         <v>0.767</v>
@@ -5633,28 +5633,28 @@
         <v>3.467499999999999</v>
       </c>
       <c r="M53">
-        <v>0.6571299</v>
+        <v>0.6700148000000001</v>
       </c>
       <c r="N53">
-        <v>2.810370099999999</v>
+        <v>2.797485199999999</v>
       </c>
       <c r="O53">
-        <v>0.4215555149999999</v>
+        <v>0.4196227799999999</v>
       </c>
       <c r="P53">
-        <v>2.388814585</v>
+        <v>2.37786242</v>
       </c>
       <c r="Q53">
-        <v>3.508814585</v>
+        <v>3.49786242</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.167999678690487</v>
+        <v>0.17034288675056</v>
       </c>
       <c r="T53">
-        <v>1.463920662852963</v>
+        <v>1.49199169162541</v>
       </c>
       <c r="U53">
         <v>0.0553</v>
@@ -5671,7 +5671,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>5.276734478221123</v>
+        <v>5.175258815178409</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5679,22 +5679,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.1062071856402688</v>
+        <v>0.1061219787221989</v>
       </c>
       <c r="C54">
-        <v>13.28470024373622</v>
+        <v>13.0697479468441</v>
       </c>
       <c r="D54">
-        <v>24.63370024373622</v>
+        <v>24.6517479468441</v>
       </c>
       <c r="E54">
-        <v>4.216000000000001</v>
+        <v>4.449</v>
       </c>
       <c r="F54">
-        <v>12.116</v>
+        <v>12.349</v>
       </c>
       <c r="G54">
         <v>0.767</v>
@@ -5715,28 +5715,28 @@
         <v>3.467499999999999</v>
       </c>
       <c r="M54">
-        <v>0.6700148000000001</v>
+        <v>0.6828997</v>
       </c>
       <c r="N54">
-        <v>2.797485199999999</v>
+        <v>2.784600299999999</v>
       </c>
       <c r="O54">
-        <v>0.4196227799999999</v>
+        <v>0.4176900449999999</v>
       </c>
       <c r="P54">
-        <v>2.37786242</v>
+        <v>2.366910254999999</v>
       </c>
       <c r="Q54">
-        <v>3.49786242</v>
+        <v>3.486910254999999</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.17034288675056</v>
+        <v>0.1727858057919126</v>
       </c>
       <c r="T54">
-        <v>1.49199169162541</v>
+        <v>1.521257232260514</v>
       </c>
       <c r="U54">
         <v>0.0553</v>
@@ -5753,7 +5753,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>5.175258815178409</v>
+        <v>5.077612422439195</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5761,22 +5761,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.1061219787221989</v>
+        <v>0.1060367718041291</v>
       </c>
       <c r="C55">
-        <v>13.0697479468441</v>
+        <v>12.85482211438041</v>
       </c>
       <c r="D55">
-        <v>24.6517479468441</v>
+        <v>24.66982211438041</v>
       </c>
       <c r="E55">
-        <v>4.449</v>
+        <v>4.682</v>
       </c>
       <c r="F55">
-        <v>12.349</v>
+        <v>12.582</v>
       </c>
       <c r="G55">
         <v>0.767</v>
@@ -5797,28 +5797,28 @@
         <v>3.467499999999999</v>
       </c>
       <c r="M55">
-        <v>0.6828997</v>
+        <v>0.6957846000000001</v>
       </c>
       <c r="N55">
-        <v>2.784600299999999</v>
+        <v>2.771715399999999</v>
       </c>
       <c r="O55">
-        <v>0.4176900449999999</v>
+        <v>0.4157573099999999</v>
       </c>
       <c r="P55">
-        <v>2.366910254999999</v>
+        <v>2.355958089999999</v>
       </c>
       <c r="Q55">
-        <v>3.486910254999999</v>
+        <v>3.475958089999999</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1727858057919126</v>
+        <v>0.1753349387046285</v>
       </c>
       <c r="T55">
-        <v>1.521257232260514</v>
+        <v>1.55179518770584</v>
       </c>
       <c r="U55">
         <v>0.0553</v>
@@ -5835,7 +5835,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>5.077612422439195</v>
+        <v>4.983582562764394</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5843,22 +5843,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.1060367718041291</v>
+        <v>0.1059515648860592</v>
       </c>
       <c r="C56">
-        <v>12.85482211438041</v>
+        <v>12.63992280459743</v>
       </c>
       <c r="D56">
-        <v>24.66982211438041</v>
+        <v>24.68792280459743</v>
       </c>
       <c r="E56">
-        <v>4.682</v>
+        <v>4.915000000000001</v>
       </c>
       <c r="F56">
-        <v>12.582</v>
+        <v>12.815</v>
       </c>
       <c r="G56">
         <v>0.767</v>
@@ -5879,28 +5879,28 @@
         <v>3.467499999999999</v>
       </c>
       <c r="M56">
-        <v>0.6957846000000001</v>
+        <v>0.7086695000000001</v>
       </c>
       <c r="N56">
-        <v>2.771715399999999</v>
+        <v>2.758830499999999</v>
       </c>
       <c r="O56">
-        <v>0.4157573099999999</v>
+        <v>0.4138245749999999</v>
       </c>
       <c r="P56">
-        <v>2.355958089999999</v>
+        <v>2.345005924999999</v>
       </c>
       <c r="Q56">
-        <v>3.475958089999999</v>
+        <v>3.465005924999999</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1753349387046285</v>
+        <v>0.177997366413465</v>
       </c>
       <c r="T56">
-        <v>1.55179518770584</v>
+        <v>1.583690385615403</v>
       </c>
       <c r="U56">
         <v>0.0553</v>
@@ -5917,7 +5917,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>4.983582562764394</v>
+        <v>4.892971970714132</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5925,22 +5925,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.1059515648860592</v>
+        <v>0.1058663579679894</v>
       </c>
       <c r="C57">
-        <v>12.63992280459743</v>
+        <v>12.42505007591852</v>
       </c>
       <c r="D57">
-        <v>24.68792280459743</v>
+        <v>24.70605007591853</v>
       </c>
       <c r="E57">
-        <v>4.915000000000001</v>
+        <v>5.148000000000001</v>
       </c>
       <c r="F57">
-        <v>12.815</v>
+        <v>13.048</v>
       </c>
       <c r="G57">
         <v>0.767</v>
@@ -5961,28 +5961,28 @@
         <v>3.467499999999999</v>
       </c>
       <c r="M57">
-        <v>0.7086695000000001</v>
+        <v>0.7215544000000002</v>
       </c>
       <c r="N57">
-        <v>2.758830499999999</v>
+        <v>2.745945599999999</v>
       </c>
       <c r="O57">
-        <v>0.4138245749999999</v>
+        <v>0.4118918399999999</v>
       </c>
       <c r="P57">
-        <v>2.345005924999999</v>
+        <v>2.334053759999999</v>
       </c>
       <c r="Q57">
-        <v>3.465005924999999</v>
+        <v>3.454053759999999</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.177997366413465</v>
+        <v>0.1807808135636122</v>
       </c>
       <c r="T57">
-        <v>1.583690385615403</v>
+        <v>1.617035365248127</v>
       </c>
       <c r="U57">
         <v>0.0553</v>
@@ -5999,7 +5999,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>4.892971970714132</v>
+        <v>4.805597471237094</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6007,22 +6007,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1058663579679894</v>
+        <v>0.1057811510499195</v>
       </c>
       <c r="C58">
-        <v>12.42505007591852</v>
+        <v>12.21020398693876</v>
       </c>
       <c r="D58">
-        <v>24.70605007591853</v>
+        <v>24.72420398693876</v>
       </c>
       <c r="E58">
-        <v>5.148000000000001</v>
+        <v>5.381000000000002</v>
       </c>
       <c r="F58">
-        <v>13.048</v>
+        <v>13.281</v>
       </c>
       <c r="G58">
         <v>0.767</v>
@@ -6043,28 +6043,28 @@
         <v>3.467499999999999</v>
       </c>
       <c r="M58">
-        <v>0.7215544000000002</v>
+        <v>0.7344393000000001</v>
       </c>
       <c r="N58">
-        <v>2.745945599999999</v>
+        <v>2.733060699999999</v>
       </c>
       <c r="O58">
-        <v>0.4118918399999999</v>
+        <v>0.4099591049999999</v>
       </c>
       <c r="P58">
-        <v>2.334053759999999</v>
+        <v>2.323101594999999</v>
       </c>
       <c r="Q58">
-        <v>3.454053759999999</v>
+        <v>3.443101594999999</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1807808135636122</v>
+        <v>0.1836937233719059</v>
       </c>
       <c r="T58">
-        <v>1.617035365248127</v>
+        <v>1.651931274166095</v>
       </c>
       <c r="U58">
         <v>0.0553</v>
@@ -6081,7 +6081,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>4.805597471237094</v>
+        <v>4.721288743671531</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6089,22 +6089,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.1057811510499195</v>
+        <v>0.1056959441318497</v>
       </c>
       <c r="C59">
-        <v>12.21020398693876</v>
+        <v>11.99538459642558</v>
       </c>
       <c r="D59">
-        <v>24.72420398693876</v>
+        <v>24.74238459642558</v>
       </c>
       <c r="E59">
-        <v>5.381000000000002</v>
+        <v>5.614000000000003</v>
       </c>
       <c r="F59">
-        <v>13.281</v>
+        <v>13.514</v>
       </c>
       <c r="G59">
         <v>0.767</v>
@@ -6125,28 +6125,28 @@
         <v>3.467499999999999</v>
       </c>
       <c r="M59">
-        <v>0.7344393000000001</v>
+        <v>0.7473242000000002</v>
       </c>
       <c r="N59">
-        <v>2.733060699999999</v>
+        <v>2.720175799999999</v>
       </c>
       <c r="O59">
-        <v>0.4099591049999999</v>
+        <v>0.4080263699999998</v>
       </c>
       <c r="P59">
-        <v>2.323101594999999</v>
+        <v>2.312149429999999</v>
       </c>
       <c r="Q59">
-        <v>3.443101594999999</v>
+        <v>3.432149429999999</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1836937233719059</v>
+        <v>0.1867453431710707</v>
       </c>
       <c r="T59">
-        <v>1.651931274166095</v>
+        <v>1.688488893032537</v>
       </c>
       <c r="U59">
         <v>0.0553</v>
@@ -6163,7 +6163,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>4.721288743671531</v>
+        <v>4.639887213608228</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6171,22 +6171,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.1056959441318497</v>
+        <v>0.1056107372137798</v>
       </c>
       <c r="C60">
-        <v>11.99538459642558</v>
+        <v>11.7805919633194</v>
       </c>
       <c r="D60">
-        <v>24.74238459642558</v>
+        <v>24.7605919633194</v>
       </c>
       <c r="E60">
-        <v>5.613999999999999</v>
+        <v>5.847</v>
       </c>
       <c r="F60">
-        <v>13.514</v>
+        <v>13.747</v>
       </c>
       <c r="G60">
         <v>0.767</v>
@@ -6207,28 +6207,28 @@
         <v>3.467499999999999</v>
       </c>
       <c r="M60">
-        <v>0.7473242</v>
+        <v>0.7602091</v>
       </c>
       <c r="N60">
-        <v>2.720175799999999</v>
+        <v>2.707290899999999</v>
       </c>
       <c r="O60">
-        <v>0.4080263699999999</v>
+        <v>0.4060936349999999</v>
       </c>
       <c r="P60">
-        <v>2.312149429999999</v>
+        <v>2.301197264999999</v>
       </c>
       <c r="Q60">
-        <v>3.43214943</v>
+        <v>3.421197265</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1867453431710706</v>
+        <v>0.1899458224726337</v>
       </c>
       <c r="T60">
-        <v>1.688488893032537</v>
+        <v>1.726829810380269</v>
       </c>
       <c r="U60">
         <v>0.0553</v>
@@ -6245,7 +6245,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>4.63988721360823</v>
+        <v>4.561245057445379</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6253,22 +6253,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.1056107372137798</v>
+        <v>0.10680053029571</v>
       </c>
       <c r="C61">
-        <v>11.7805919633194</v>
+        <v>11.29575273328624</v>
       </c>
       <c r="D61">
-        <v>24.7605919633194</v>
+        <v>24.50875273328624</v>
       </c>
       <c r="E61">
-        <v>5.847</v>
+        <v>6.08</v>
       </c>
       <c r="F61">
-        <v>13.747</v>
+        <v>13.98</v>
       </c>
       <c r="G61">
         <v>0.767</v>
@@ -6289,45 +6289,45 @@
         <v>3.467499999999999</v>
       </c>
       <c r="M61">
-        <v>0.7602091</v>
+        <v>0.8080440000000001</v>
       </c>
       <c r="N61">
-        <v>2.707290899999999</v>
+        <v>2.659455999999999</v>
       </c>
       <c r="O61">
-        <v>0.4060936349999999</v>
+        <v>0.3989183999999998</v>
       </c>
       <c r="P61">
-        <v>2.301197264999999</v>
+        <v>2.260537599999999</v>
       </c>
       <c r="Q61">
-        <v>3.421197265</v>
+        <v>3.380537599999999</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1899458224726337</v>
+        <v>0.1933063257392749</v>
       </c>
       <c r="T61">
-        <v>1.726829810380269</v>
+        <v>1.767087773595387</v>
       </c>
       <c r="U61">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V61">
         <v>0.15</v>
       </c>
       <c r="W61">
-        <v>0.047005</v>
+        <v>0.04913</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y61">
-        <v>4.561245057445379</v>
+        <v>4.291226715376884</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6335,22 +6335,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.10680053029571</v>
+        <v>0.1067365733776401</v>
       </c>
       <c r="C62">
-        <v>11.29575273328624</v>
+        <v>11.07615990489155</v>
       </c>
       <c r="D62">
-        <v>24.50875273328624</v>
+        <v>24.52215990489155</v>
       </c>
       <c r="E62">
-        <v>6.08</v>
+        <v>6.313000000000001</v>
       </c>
       <c r="F62">
-        <v>13.98</v>
+        <v>14.213</v>
       </c>
       <c r="G62">
         <v>0.767</v>
@@ -6371,28 +6371,28 @@
         <v>3.467499999999999</v>
       </c>
       <c r="M62">
-        <v>0.8080440000000001</v>
+        <v>0.8215114000000001</v>
       </c>
       <c r="N62">
-        <v>2.659455999999999</v>
+        <v>2.645988599999999</v>
       </c>
       <c r="O62">
-        <v>0.3989183999999998</v>
+        <v>0.3968982899999998</v>
       </c>
       <c r="P62">
-        <v>2.260537599999999</v>
+        <v>2.249090309999999</v>
       </c>
       <c r="Q62">
-        <v>3.380537599999999</v>
+        <v>3.369090309999999</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1933063257392749</v>
+        <v>0.1968391625067695</v>
       </c>
       <c r="T62">
-        <v>1.767087773595387</v>
+        <v>1.809410247744615</v>
       </c>
       <c r="U62">
         <v>0.0578</v>
@@ -6409,7 +6409,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>4.291226715376884</v>
+        <v>4.220878736436279</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6417,22 +6417,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.1067365733776401</v>
+        <v>0.1066726164595703</v>
       </c>
       <c r="C63">
-        <v>11.07615990489155</v>
+        <v>10.85658175293814</v>
       </c>
       <c r="D63">
-        <v>24.52215990489155</v>
+        <v>24.53558175293814</v>
       </c>
       <c r="E63">
-        <v>6.313000000000001</v>
+        <v>6.545999999999999</v>
       </c>
       <c r="F63">
-        <v>14.213</v>
+        <v>14.446</v>
       </c>
       <c r="G63">
         <v>0.767</v>
@@ -6453,28 +6453,28 @@
         <v>3.467499999999999</v>
       </c>
       <c r="M63">
-        <v>0.8215114000000001</v>
+        <v>0.8349788</v>
       </c>
       <c r="N63">
-        <v>2.645988599999999</v>
+        <v>2.632521199999999</v>
       </c>
       <c r="O63">
-        <v>0.3968982899999998</v>
+        <v>0.3948781799999999</v>
       </c>
       <c r="P63">
-        <v>2.249090309999999</v>
+        <v>2.237643019999999</v>
       </c>
       <c r="Q63">
-        <v>3.369090309999999</v>
+        <v>3.357643019999999</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1968391625067695</v>
+        <v>0.2005579380515007</v>
       </c>
       <c r="T63">
-        <v>1.809410247744615</v>
+        <v>1.853960220533275</v>
       </c>
       <c r="U63">
         <v>0.0578</v>
@@ -6491,7 +6491,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>4.220878736436279</v>
+        <v>4.15280004713892</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6499,22 +6499,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.1066726164595703</v>
+        <v>0.1066086595415004</v>
       </c>
       <c r="C64">
-        <v>10.85658175293814</v>
+        <v>10.63701830153802</v>
       </c>
       <c r="D64">
-        <v>24.53558175293814</v>
+        <v>24.54901830153802</v>
       </c>
       <c r="E64">
-        <v>6.545999999999999</v>
+        <v>6.779</v>
       </c>
       <c r="F64">
-        <v>14.446</v>
+        <v>14.679</v>
       </c>
       <c r="G64">
         <v>0.767</v>
@@ -6535,28 +6535,28 @@
         <v>3.467499999999999</v>
       </c>
       <c r="M64">
-        <v>0.8349788</v>
+        <v>0.8484462</v>
       </c>
       <c r="N64">
-        <v>2.632521199999999</v>
+        <v>2.619053799999999</v>
       </c>
       <c r="O64">
-        <v>0.3948781799999999</v>
+        <v>0.3928580699999999</v>
       </c>
       <c r="P64">
-        <v>2.237643019999999</v>
+        <v>2.226195729999999</v>
       </c>
       <c r="Q64">
-        <v>3.357643019999999</v>
+        <v>3.346195729999999</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.2005579380515007</v>
+        <v>0.2044777284905417</v>
       </c>
       <c r="T64">
-        <v>1.853960220533275</v>
+        <v>1.900918299959161</v>
       </c>
       <c r="U64">
         <v>0.0578</v>
@@ -6573,7 +6573,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>4.15280004713892</v>
+        <v>4.086882586073223</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6581,22 +6581,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.1066086595415004</v>
+        <v>0.1065447026234305</v>
       </c>
       <c r="C65">
-        <v>10.63701830153802</v>
+        <v>10.41746957485606</v>
       </c>
       <c r="D65">
-        <v>24.54901830153802</v>
+        <v>24.56246957485606</v>
       </c>
       <c r="E65">
-        <v>6.779</v>
+        <v>7.012</v>
       </c>
       <c r="F65">
-        <v>14.679</v>
+        <v>14.912</v>
       </c>
       <c r="G65">
         <v>0.767</v>
@@ -6617,28 +6617,28 @@
         <v>3.467499999999999</v>
       </c>
       <c r="M65">
-        <v>0.8484462</v>
+        <v>0.8619136000000001</v>
       </c>
       <c r="N65">
-        <v>2.619053799999999</v>
+        <v>2.605586399999999</v>
       </c>
       <c r="O65">
-        <v>0.3928580699999999</v>
+        <v>0.3908379599999999</v>
       </c>
       <c r="P65">
-        <v>2.226195729999999</v>
+        <v>2.214748439999999</v>
       </c>
       <c r="Q65">
-        <v>3.346195729999999</v>
+        <v>3.334748439999999</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.2044777284905417</v>
+        <v>0.2086152850650849</v>
       </c>
       <c r="T65">
-        <v>1.900918299959161</v>
+        <v>1.950485161575373</v>
       </c>
       <c r="U65">
         <v>0.0578</v>
@@ -6655,7 +6655,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>4.086882586073223</v>
+        <v>4.023025045665829</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6663,22 +6663,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.1065447026234305</v>
+        <v>0.1084144957053607</v>
       </c>
       <c r="C66">
-        <v>10.41746957485606</v>
+        <v>9.797207034282406</v>
       </c>
       <c r="D66">
-        <v>24.56246957485606</v>
+        <v>24.17520703428241</v>
       </c>
       <c r="E66">
-        <v>7.012</v>
+        <v>7.245000000000001</v>
       </c>
       <c r="F66">
-        <v>14.912</v>
+        <v>15.145</v>
       </c>
       <c r="G66">
         <v>0.767</v>
@@ -6699,45 +6699,45 @@
         <v>3.467499999999999</v>
       </c>
       <c r="M66">
-        <v>0.8619136000000001</v>
+        <v>0.9283885000000001</v>
       </c>
       <c r="N66">
-        <v>2.605586399999999</v>
+        <v>2.539111499999999</v>
       </c>
       <c r="O66">
-        <v>0.3908379599999999</v>
+        <v>0.3808667249999999</v>
       </c>
       <c r="P66">
-        <v>2.214748439999999</v>
+        <v>2.158244775</v>
       </c>
       <c r="Q66">
-        <v>3.334748439999999</v>
+        <v>3.278244775</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.2086152850650849</v>
+        <v>0.2129892734438878</v>
       </c>
       <c r="T66">
-        <v>1.950485161575373</v>
+        <v>2.00288441528394</v>
       </c>
       <c r="U66">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V66">
         <v>0.15</v>
       </c>
       <c r="W66">
-        <v>0.04913</v>
+        <v>0.052105</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y66">
-        <v>4.023025045665829</v>
+        <v>3.734966557642624</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6745,22 +6745,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.1084144957053607</v>
+        <v>0.1083802887872909</v>
       </c>
       <c r="C67">
-        <v>9.797207034282406</v>
+        <v>9.571182116752487</v>
       </c>
       <c r="D67">
-        <v>24.17520703428241</v>
+        <v>24.18218211675249</v>
       </c>
       <c r="E67">
-        <v>7.245000000000001</v>
+        <v>7.478000000000002</v>
       </c>
       <c r="F67">
-        <v>15.145</v>
+        <v>15.378</v>
       </c>
       <c r="G67">
         <v>0.767</v>
@@ -6781,28 +6781,28 @@
         <v>3.467499999999999</v>
       </c>
       <c r="M67">
-        <v>0.9283885000000001</v>
+        <v>0.9426714000000002</v>
       </c>
       <c r="N67">
-        <v>2.539111499999999</v>
+        <v>2.524828599999999</v>
       </c>
       <c r="O67">
-        <v>0.3808667249999999</v>
+        <v>0.3787242899999999</v>
       </c>
       <c r="P67">
-        <v>2.158244775</v>
+        <v>2.146104309999999</v>
       </c>
       <c r="Q67">
-        <v>3.278244775</v>
+        <v>3.266104309999999</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.2129892734438878</v>
+        <v>0.2176205552567378</v>
       </c>
       <c r="T67">
-        <v>2.00288441528394</v>
+        <v>2.058365978034188</v>
       </c>
       <c r="U67">
         <v>0.0613</v>
@@ -6819,7 +6819,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>3.734966557642624</v>
+        <v>3.678376155254099</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6827,22 +6827,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.1083802887872909</v>
+        <v>0.108346081869221</v>
       </c>
       <c r="C68">
-        <v>9.571182116752487</v>
+        <v>9.345161225315632</v>
       </c>
       <c r="D68">
-        <v>24.18218211675249</v>
+        <v>24.18916122531563</v>
       </c>
       <c r="E68">
-        <v>7.478000000000002</v>
+        <v>7.711</v>
       </c>
       <c r="F68">
-        <v>15.378</v>
+        <v>15.611</v>
       </c>
       <c r="G68">
         <v>0.767</v>
@@ -6863,28 +6863,28 @@
         <v>3.467499999999999</v>
       </c>
       <c r="M68">
-        <v>0.9426714000000002</v>
+        <v>0.9569543</v>
       </c>
       <c r="N68">
-        <v>2.524828599999999</v>
+        <v>2.510545699999999</v>
       </c>
       <c r="O68">
-        <v>0.3787242899999999</v>
+        <v>0.3765818549999999</v>
       </c>
       <c r="P68">
-        <v>2.146104309999999</v>
+        <v>2.133963844999999</v>
       </c>
       <c r="Q68">
-        <v>3.266104309999999</v>
+        <v>3.253963844999999</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.2176205552567378</v>
+        <v>0.2225325208158213</v>
       </c>
       <c r="T68">
-        <v>2.058365978034188</v>
+        <v>2.117210059738996</v>
       </c>
       <c r="U68">
         <v>0.0613</v>
@@ -6901,7 +6901,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>3.678376155254099</v>
+        <v>3.623475018608516</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6909,22 +6909,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.108346081869221</v>
+        <v>0.1083118749511512</v>
       </c>
       <c r="C69">
-        <v>9.345161225315632</v>
+        <v>9.119144363458698</v>
       </c>
       <c r="D69">
-        <v>24.18916122531563</v>
+        <v>24.1961443634587</v>
       </c>
       <c r="E69">
-        <v>7.711</v>
+        <v>7.944000000000001</v>
       </c>
       <c r="F69">
-        <v>15.611</v>
+        <v>15.844</v>
       </c>
       <c r="G69">
         <v>0.767</v>
@@ -6945,28 +6945,28 @@
         <v>3.467499999999999</v>
       </c>
       <c r="M69">
-        <v>0.9569543</v>
+        <v>0.9712372000000001</v>
       </c>
       <c r="N69">
-        <v>2.510545699999999</v>
+        <v>2.496262799999999</v>
       </c>
       <c r="O69">
-        <v>0.3765818549999999</v>
+        <v>0.3744394199999999</v>
       </c>
       <c r="P69">
-        <v>2.133963844999999</v>
+        <v>2.121823379999999</v>
       </c>
       <c r="Q69">
-        <v>3.253963844999999</v>
+        <v>3.24182338</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.2225325208158213</v>
+        <v>0.2277514842223474</v>
       </c>
       <c r="T69">
-        <v>2.117210059738996</v>
+        <v>2.179731896550355</v>
       </c>
       <c r="U69">
         <v>0.0613</v>
@@ -6983,7 +6983,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>3.623475018608516</v>
+        <v>3.570188621276037</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6991,22 +6991,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.1083118749511512</v>
+        <v>0.1082776680330813</v>
       </c>
       <c r="C70">
-        <v>9.119144363458698</v>
+        <v>8.893131534672573</v>
       </c>
       <c r="D70">
-        <v>24.1961443634587</v>
+        <v>24.20313153467258</v>
       </c>
       <c r="E70">
-        <v>7.944000000000001</v>
+        <v>8.177000000000001</v>
       </c>
       <c r="F70">
-        <v>15.844</v>
+        <v>16.077</v>
       </c>
       <c r="G70">
         <v>0.767</v>
@@ -7027,28 +7027,28 @@
         <v>3.467499999999999</v>
       </c>
       <c r="M70">
-        <v>0.9712372000000001</v>
+        <v>0.9855201000000001</v>
       </c>
       <c r="N70">
-        <v>2.496262799999999</v>
+        <v>2.481979899999999</v>
       </c>
       <c r="O70">
-        <v>0.3744394199999999</v>
+        <v>0.3722969849999999</v>
       </c>
       <c r="P70">
-        <v>2.121823379999999</v>
+        <v>2.109682915</v>
       </c>
       <c r="Q70">
-        <v>3.24182338</v>
+        <v>3.229682915</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.2277514842223474</v>
+        <v>0.2333071549454236</v>
       </c>
       <c r="T70">
-        <v>2.179731896550355</v>
+        <v>2.246287400252769</v>
       </c>
       <c r="U70">
         <v>0.0613</v>
@@ -7065,7 +7065,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>3.570188621276037</v>
+        <v>3.518446757199573</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7073,22 +7073,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.1082776680330813</v>
+        <v>0.1099094611150115</v>
       </c>
       <c r="C71">
-        <v>8.893131534672573</v>
+        <v>8.33125253570369</v>
       </c>
       <c r="D71">
-        <v>24.20313153467258</v>
+        <v>23.87425253570369</v>
       </c>
       <c r="E71">
-        <v>8.177000000000001</v>
+        <v>8.410000000000002</v>
       </c>
       <c r="F71">
-        <v>16.077</v>
+        <v>16.31</v>
       </c>
       <c r="G71">
         <v>0.767</v>
@@ -7109,45 +7109,45 @@
         <v>3.467499999999999</v>
       </c>
       <c r="M71">
-        <v>0.9855201000000001</v>
+        <v>1.045471</v>
       </c>
       <c r="N71">
-        <v>2.481979899999999</v>
+        <v>2.422028999999999</v>
       </c>
       <c r="O71">
-        <v>0.3722969849999999</v>
+        <v>0.3633043499999999</v>
       </c>
       <c r="P71">
-        <v>2.109682915</v>
+        <v>2.058724649999999</v>
       </c>
       <c r="Q71">
-        <v>3.229682915</v>
+        <v>3.178724649999999</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.2333071549454236</v>
+        <v>0.2392332037167049</v>
       </c>
       <c r="T71">
-        <v>2.246287400252769</v>
+        <v>2.317279937535344</v>
       </c>
       <c r="U71">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V71">
         <v>0.15</v>
       </c>
       <c r="W71">
-        <v>0.052105</v>
+        <v>0.054485</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y71">
-        <v>3.518446757199573</v>
+        <v>3.3166869286666</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7155,22 +7155,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.1099094611150115</v>
+        <v>0.1098990541969416</v>
       </c>
       <c r="C72">
-        <v>8.33125253570369</v>
+        <v>8.100321671766434</v>
       </c>
       <c r="D72">
-        <v>23.87425253570369</v>
+        <v>23.87632167176644</v>
       </c>
       <c r="E72">
-        <v>8.410000000000002</v>
+        <v>8.643000000000002</v>
       </c>
       <c r="F72">
-        <v>16.31</v>
+        <v>16.543</v>
       </c>
       <c r="G72">
         <v>0.767</v>
@@ -7191,28 +7191,28 @@
         <v>3.467499999999999</v>
       </c>
       <c r="M72">
-        <v>1.045471</v>
+        <v>1.0604063</v>
       </c>
       <c r="N72">
-        <v>2.422028999999999</v>
+        <v>2.407093699999999</v>
       </c>
       <c r="O72">
-        <v>0.3633043499999999</v>
+        <v>0.3610640549999998</v>
       </c>
       <c r="P72">
-        <v>2.058724649999999</v>
+        <v>2.046029644999999</v>
       </c>
       <c r="Q72">
-        <v>3.178724649999999</v>
+        <v>3.166029644999999</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.2392332037167049</v>
+        <v>0.2455679455066953</v>
       </c>
       <c r="T72">
-        <v>2.317279937535344</v>
+        <v>2.39316851187189</v>
       </c>
       <c r="U72">
         <v>0.0641</v>
@@ -7229,7 +7229,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>3.3166869286666</v>
+        <v>3.269973028262844</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7237,22 +7237,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.1098990541969416</v>
+        <v>0.1098886472788717</v>
       </c>
       <c r="C73">
-        <v>8.10032167176643</v>
+        <v>7.869391166516444</v>
       </c>
       <c r="D73">
-        <v>23.87632167176643</v>
+        <v>23.87839116651644</v>
       </c>
       <c r="E73">
-        <v>8.642999999999999</v>
+        <v>8.875999999999999</v>
       </c>
       <c r="F73">
-        <v>16.543</v>
+        <v>16.776</v>
       </c>
       <c r="G73">
         <v>0.767</v>
@@ -7273,28 +7273,28 @@
         <v>3.467499999999999</v>
       </c>
       <c r="M73">
-        <v>1.0604063</v>
+        <v>1.0753416</v>
       </c>
       <c r="N73">
-        <v>2.407093699999999</v>
+        <v>2.3921584</v>
       </c>
       <c r="O73">
-        <v>0.3610640549999999</v>
+        <v>0.3588237599999999</v>
       </c>
       <c r="P73">
-        <v>2.046029645</v>
+        <v>2.03333464</v>
       </c>
       <c r="Q73">
-        <v>3.166029645</v>
+        <v>3.15333464</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.2455679455066952</v>
+        <v>0.2523551688531134</v>
       </c>
       <c r="T73">
-        <v>2.393168511871889</v>
+        <v>2.474477698661045</v>
       </c>
       <c r="U73">
         <v>0.0641</v>
@@ -7311,7 +7311,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>3.269973028262846</v>
+        <v>3.22455673620364</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7319,22 +7319,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.1098886472788717</v>
+        <v>0.1098782403608019</v>
       </c>
       <c r="C74">
-        <v>7.869391166516444</v>
+        <v>7.638461020046979</v>
       </c>
       <c r="D74">
-        <v>23.87839116651644</v>
+        <v>23.88046102004698</v>
       </c>
       <c r="E74">
-        <v>8.875999999999999</v>
+        <v>9.109</v>
       </c>
       <c r="F74">
-        <v>16.776</v>
+        <v>17.009</v>
       </c>
       <c r="G74">
         <v>0.767</v>
@@ -7355,28 +7355,28 @@
         <v>3.467499999999999</v>
       </c>
       <c r="M74">
-        <v>1.0753416</v>
+        <v>1.0902769</v>
       </c>
       <c r="N74">
-        <v>2.3921584</v>
+        <v>2.377223099999999</v>
       </c>
       <c r="O74">
-        <v>0.3588237599999999</v>
+        <v>0.3565834649999999</v>
       </c>
       <c r="P74">
-        <v>2.03333464</v>
+        <v>2.020639634999999</v>
       </c>
       <c r="Q74">
-        <v>3.15333464</v>
+        <v>3.140639634999999</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.2523551688531134</v>
+        <v>0.2596451494844514</v>
       </c>
       <c r="T74">
-        <v>2.474477698661045</v>
+        <v>2.561809788175323</v>
       </c>
       <c r="U74">
         <v>0.0641</v>
@@ -7393,7 +7393,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>3.22455673620364</v>
+        <v>3.180384726118658</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7401,22 +7401,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.1098782403608019</v>
+        <v>0.109867833442732</v>
       </c>
       <c r="C75">
-        <v>7.638461020046979</v>
+        <v>7.407531232451369</v>
       </c>
       <c r="D75">
-        <v>23.88046102004698</v>
+        <v>23.88253123245137</v>
       </c>
       <c r="E75">
-        <v>9.109</v>
+        <v>9.342000000000001</v>
       </c>
       <c r="F75">
-        <v>17.009</v>
+        <v>17.242</v>
       </c>
       <c r="G75">
         <v>0.767</v>
@@ -7437,28 +7437,28 @@
         <v>3.467499999999999</v>
       </c>
       <c r="M75">
-        <v>1.0902769</v>
+        <v>1.1052122</v>
       </c>
       <c r="N75">
-        <v>2.377223099999999</v>
+        <v>2.362287799999999</v>
       </c>
       <c r="O75">
-        <v>0.3565834649999999</v>
+        <v>0.3543431699999998</v>
       </c>
       <c r="P75">
-        <v>2.020639634999999</v>
+        <v>2.007944629999999</v>
       </c>
       <c r="Q75">
-        <v>3.140639634999999</v>
+        <v>3.127944629999999</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.2596451494844514</v>
+        <v>0.2674958978566617</v>
       </c>
       <c r="T75">
-        <v>2.561809788175323</v>
+        <v>2.655859730729162</v>
       </c>
       <c r="U75">
         <v>0.0641</v>
@@ -7475,7 +7475,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>3.180384726118658</v>
+        <v>3.137406554144081</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7483,22 +7483,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.109867833442732</v>
+        <v>0.1098574265246622</v>
       </c>
       <c r="C76">
-        <v>7.407531232451369</v>
+        <v>7.176601803822944</v>
       </c>
       <c r="D76">
-        <v>23.88253123245137</v>
+        <v>23.88460180382295</v>
       </c>
       <c r="E76">
-        <v>9.342000000000001</v>
+        <v>9.575000000000001</v>
       </c>
       <c r="F76">
-        <v>17.242</v>
+        <v>17.475</v>
       </c>
       <c r="G76">
         <v>0.767</v>
@@ -7519,28 +7519,28 @@
         <v>3.467499999999999</v>
       </c>
       <c r="M76">
-        <v>1.1052122</v>
+        <v>1.1201475</v>
       </c>
       <c r="N76">
-        <v>2.362287799999999</v>
+        <v>2.3473525</v>
       </c>
       <c r="O76">
-        <v>0.3543431699999998</v>
+        <v>0.3521028749999999</v>
       </c>
       <c r="P76">
-        <v>2.007944629999999</v>
+        <v>1.995249625</v>
       </c>
       <c r="Q76">
-        <v>3.127944629999999</v>
+        <v>3.115249625</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.2674958978566617</v>
+        <v>0.2759747060986488</v>
       </c>
       <c r="T76">
-        <v>2.655859730729162</v>
+        <v>2.757433668687308</v>
       </c>
       <c r="U76">
         <v>0.0641</v>
@@ -7557,7 +7557,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>3.137406554144081</v>
+        <v>3.095574466755494</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7565,22 +7565,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.1098574265246622</v>
+        <v>0.1098470196065923</v>
       </c>
       <c r="C77">
-        <v>7.176601803822944</v>
+        <v>6.945672734255073</v>
       </c>
       <c r="D77">
-        <v>23.88460180382295</v>
+        <v>23.88667273425508</v>
       </c>
       <c r="E77">
-        <v>9.575000000000001</v>
+        <v>9.808000000000002</v>
       </c>
       <c r="F77">
-        <v>17.475</v>
+        <v>17.708</v>
       </c>
       <c r="G77">
         <v>0.767</v>
@@ -7601,28 +7601,28 @@
         <v>3.467499999999999</v>
       </c>
       <c r="M77">
-        <v>1.1201475</v>
+        <v>1.1350828</v>
       </c>
       <c r="N77">
-        <v>2.3473525</v>
+        <v>2.332417199999999</v>
       </c>
       <c r="O77">
-        <v>0.3521028749999999</v>
+        <v>0.3498625799999999</v>
       </c>
       <c r="P77">
-        <v>1.995249625</v>
+        <v>1.982554619999999</v>
       </c>
       <c r="Q77">
-        <v>3.115249625</v>
+        <v>3.102554619999999</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.2759747060986488</v>
+        <v>0.2851600816941348</v>
       </c>
       <c r="T77">
-        <v>2.757433668687308</v>
+        <v>2.8674721014753</v>
       </c>
       <c r="U77">
         <v>0.0641</v>
@@ -7639,7 +7639,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>3.095574466755494</v>
+        <v>3.054843223771868</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7647,22 +7647,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.1098470196065923</v>
+        <v>0.1098366126885225</v>
       </c>
       <c r="C78">
-        <v>6.945672734255073</v>
+        <v>6.714744023841181</v>
       </c>
       <c r="D78">
-        <v>23.88667273425508</v>
+        <v>23.88874402384118</v>
       </c>
       <c r="E78">
-        <v>9.808000000000002</v>
+        <v>10.041</v>
       </c>
       <c r="F78">
-        <v>17.708</v>
+        <v>17.941</v>
       </c>
       <c r="G78">
         <v>0.767</v>
@@ -7683,28 +7683,28 @@
         <v>3.467499999999999</v>
       </c>
       <c r="M78">
-        <v>1.1350828</v>
+        <v>1.1500181</v>
       </c>
       <c r="N78">
-        <v>2.332417199999999</v>
+        <v>2.317481899999999</v>
       </c>
       <c r="O78">
-        <v>0.3498625799999999</v>
+        <v>0.3476222849999998</v>
       </c>
       <c r="P78">
-        <v>1.982554619999999</v>
+        <v>1.969859614999999</v>
       </c>
       <c r="Q78">
-        <v>3.102554619999999</v>
+        <v>3.089859614999999</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.2851600816941348</v>
+        <v>0.2951441856022717</v>
       </c>
       <c r="T78">
-        <v>2.8674721014753</v>
+        <v>2.987079093636159</v>
       </c>
       <c r="U78">
         <v>0.0641</v>
@@ -7721,7 +7721,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>3.054843223771868</v>
+        <v>3.015169935151454</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7729,22 +7729,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.1098366126885225</v>
+        <v>0.1149976057704526</v>
       </c>
       <c r="C79">
-        <v>6.714744023841181</v>
+        <v>5.496816749623068</v>
       </c>
       <c r="D79">
-        <v>23.88874402384118</v>
+        <v>22.90381674962307</v>
       </c>
       <c r="E79">
-        <v>10.041</v>
+        <v>10.274</v>
       </c>
       <c r="F79">
-        <v>17.941</v>
+        <v>18.174</v>
       </c>
       <c r="G79">
         <v>0.767</v>
@@ -7765,45 +7765,45 @@
         <v>3.467499999999999</v>
       </c>
       <c r="M79">
-        <v>1.1500181</v>
+        <v>1.3067106</v>
       </c>
       <c r="N79">
-        <v>2.317481899999999</v>
+        <v>2.160789399999999</v>
       </c>
       <c r="O79">
-        <v>0.3476222849999998</v>
+        <v>0.3241184099999999</v>
       </c>
       <c r="P79">
-        <v>1.969859614999999</v>
+        <v>1.836670989999999</v>
       </c>
       <c r="Q79">
-        <v>3.089859614999999</v>
+        <v>2.956670989999999</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.2951441856022717</v>
+        <v>0.3060359353202393</v>
       </c>
       <c r="T79">
-        <v>2.987079093636159</v>
+        <v>3.117559448720734</v>
       </c>
       <c r="U79">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V79">
         <v>0.15</v>
       </c>
       <c r="W79">
-        <v>0.054485</v>
+        <v>0.061115</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y79">
-        <v>3.015169935151454</v>
+        <v>2.653609758733111</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7811,22 +7811,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.1149976057704526</v>
+        <v>0.1150534988523828</v>
       </c>
       <c r="C80">
-        <v>5.496816749623068</v>
+        <v>5.253594426326057</v>
       </c>
       <c r="D80">
-        <v>22.90381674962307</v>
+        <v>22.89359442632606</v>
       </c>
       <c r="E80">
-        <v>10.274</v>
+        <v>10.507</v>
       </c>
       <c r="F80">
-        <v>18.174</v>
+        <v>18.407</v>
       </c>
       <c r="G80">
         <v>0.767</v>
@@ -7847,28 +7847,28 @@
         <v>3.467499999999999</v>
       </c>
       <c r="M80">
-        <v>1.3067106</v>
+        <v>1.3234633</v>
       </c>
       <c r="N80">
-        <v>2.160789399999999</v>
+        <v>2.144036699999999</v>
       </c>
       <c r="O80">
-        <v>0.3241184099999999</v>
+        <v>0.3216055049999998</v>
       </c>
       <c r="P80">
-        <v>1.836670989999999</v>
+        <v>1.822431194999999</v>
       </c>
       <c r="Q80">
-        <v>2.956670989999999</v>
+        <v>2.942431194999999</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.3060359353202393</v>
+        <v>0.3179649945351561</v>
       </c>
       <c r="T80">
-        <v>3.117559448720734</v>
+        <v>3.260466504289554</v>
       </c>
       <c r="U80">
         <v>0.07190000000000001</v>
@@ -7885,7 +7885,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>2.653609758733111</v>
+        <v>2.620019761787122</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7893,22 +7893,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.1150534988523828</v>
+        <v>0.1151093919343129</v>
       </c>
       <c r="C81">
-        <v>5.253594426326057</v>
+        <v>5.010381223716426</v>
       </c>
       <c r="D81">
-        <v>22.89359442632606</v>
+        <v>22.88338122371643</v>
       </c>
       <c r="E81">
-        <v>10.507</v>
+        <v>10.74</v>
       </c>
       <c r="F81">
-        <v>18.407</v>
+        <v>18.64</v>
       </c>
       <c r="G81">
         <v>0.767</v>
@@ -7929,28 +7929,28 @@
         <v>3.467499999999999</v>
       </c>
       <c r="M81">
-        <v>1.3234633</v>
+        <v>1.340216</v>
       </c>
       <c r="N81">
-        <v>2.144036699999999</v>
+        <v>2.127284</v>
       </c>
       <c r="O81">
-        <v>0.3216055049999998</v>
+        <v>0.3190925999999999</v>
       </c>
       <c r="P81">
-        <v>1.822431194999999</v>
+        <v>1.8081914</v>
       </c>
       <c r="Q81">
-        <v>2.942431194999999</v>
+        <v>2.9281914</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.3179649945351561</v>
+        <v>0.3310869596715647</v>
       </c>
       <c r="T81">
-        <v>3.260466504289554</v>
+        <v>3.417664265415255</v>
       </c>
       <c r="U81">
         <v>0.07190000000000001</v>
@@ -7967,7 +7967,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>2.620019761787122</v>
+        <v>2.587269514764784</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7975,22 +7975,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.1151093919343129</v>
+        <v>0.1151652850162431</v>
       </c>
       <c r="C82">
-        <v>5.010381223716426</v>
+        <v>4.767177129592966</v>
       </c>
       <c r="D82">
-        <v>22.88338122371643</v>
+        <v>22.87317712959297</v>
       </c>
       <c r="E82">
-        <v>10.74</v>
+        <v>10.973</v>
       </c>
       <c r="F82">
-        <v>18.64</v>
+        <v>18.873</v>
       </c>
       <c r="G82">
         <v>0.767</v>
@@ -8011,28 +8011,28 @@
         <v>3.467499999999999</v>
       </c>
       <c r="M82">
-        <v>1.340216</v>
+        <v>1.3569687</v>
       </c>
       <c r="N82">
-        <v>2.127284</v>
+        <v>2.110531299999999</v>
       </c>
       <c r="O82">
-        <v>0.3190925999999999</v>
+        <v>0.3165796949999998</v>
       </c>
       <c r="P82">
-        <v>1.8081914</v>
+        <v>1.793951604999999</v>
       </c>
       <c r="Q82">
-        <v>2.9281914</v>
+        <v>2.913951604999999</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.3310869596715647</v>
+        <v>0.3455901842960163</v>
       </c>
       <c r="T82">
-        <v>3.417664265415255</v>
+        <v>3.591409159291032</v>
       </c>
       <c r="U82">
         <v>0.07190000000000001</v>
@@ -8049,7 +8049,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>2.587269514764784</v>
+        <v>2.55532791581707</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8057,22 +8057,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.1151652850162431</v>
+        <v>0.1152211780981732</v>
       </c>
       <c r="C83">
-        <v>4.767177129592966</v>
+        <v>4.523982131776226</v>
       </c>
       <c r="D83">
-        <v>22.87317712959297</v>
+        <v>22.86298213177623</v>
       </c>
       <c r="E83">
-        <v>10.973</v>
+        <v>11.206</v>
       </c>
       <c r="F83">
-        <v>18.873</v>
+        <v>19.106</v>
       </c>
       <c r="G83">
         <v>0.767</v>
@@ -8093,28 +8093,28 @@
         <v>3.467499999999999</v>
       </c>
       <c r="M83">
-        <v>1.3569687</v>
+        <v>1.3737214</v>
       </c>
       <c r="N83">
-        <v>2.110531299999999</v>
+        <v>2.093778599999999</v>
       </c>
       <c r="O83">
-        <v>0.3165796949999998</v>
+        <v>0.3140667899999999</v>
       </c>
       <c r="P83">
-        <v>1.793951604999999</v>
+        <v>1.77971181</v>
       </c>
       <c r="Q83">
-        <v>2.913951604999999</v>
+        <v>2.899711809999999</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.3455901842960163</v>
+        <v>0.3617048783231847</v>
       </c>
       <c r="T83">
-        <v>3.591409159291032</v>
+        <v>3.784459041375227</v>
       </c>
       <c r="U83">
         <v>0.07190000000000001</v>
@@ -8131,7 +8131,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>2.55532791581707</v>
+        <v>2.524165380258325</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8139,22 +8139,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.1152211780981732</v>
+        <v>0.1180285211801034</v>
       </c>
       <c r="C84">
-        <v>4.523982131776226</v>
+        <v>3.790353610835332</v>
       </c>
       <c r="D84">
-        <v>22.86298213177623</v>
+        <v>22.36235361083533</v>
       </c>
       <c r="E84">
-        <v>11.206</v>
+        <v>11.439</v>
       </c>
       <c r="F84">
-        <v>19.106</v>
+        <v>19.339</v>
       </c>
       <c r="G84">
         <v>0.767</v>
@@ -8175,45 +8175,45 @@
         <v>3.467499999999999</v>
       </c>
       <c r="M84">
-        <v>1.3737214</v>
+        <v>1.4658962</v>
       </c>
       <c r="N84">
-        <v>2.093778599999999</v>
+        <v>2.001603799999999</v>
       </c>
       <c r="O84">
-        <v>0.3140667899999999</v>
+        <v>0.3002405699999998</v>
       </c>
       <c r="P84">
-        <v>1.77971181</v>
+        <v>1.701363229999999</v>
       </c>
       <c r="Q84">
-        <v>2.899711809999999</v>
+        <v>2.821363229999999</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.3617048783231847</v>
+        <v>0.3797154187064906</v>
       </c>
       <c r="T84">
-        <v>3.784459041375227</v>
+        <v>4.000220674292857</v>
       </c>
       <c r="U84">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V84">
         <v>0.15</v>
       </c>
       <c r="W84">
-        <v>0.061115</v>
+        <v>0.06443</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y84">
-        <v>2.524165380258325</v>
+        <v>2.365447157854696</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8221,22 +8221,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.1180285211801034</v>
+        <v>0.1181175642620335</v>
       </c>
       <c r="C85">
-        <v>3.790353610835332</v>
+        <v>3.541833193645562</v>
       </c>
       <c r="D85">
-        <v>22.36235361083533</v>
+        <v>22.34683319364557</v>
       </c>
       <c r="E85">
-        <v>11.439</v>
+        <v>11.672</v>
       </c>
       <c r="F85">
-        <v>19.339</v>
+        <v>19.572</v>
       </c>
       <c r="G85">
         <v>0.767</v>
@@ -8257,28 +8257,28 @@
         <v>3.467499999999999</v>
       </c>
       <c r="M85">
-        <v>1.4658962</v>
+        <v>1.4835576</v>
       </c>
       <c r="N85">
-        <v>2.001603799999999</v>
+        <v>1.983942399999999</v>
       </c>
       <c r="O85">
-        <v>0.3002405699999998</v>
+        <v>0.2975913599999999</v>
       </c>
       <c r="P85">
-        <v>1.701363229999999</v>
+        <v>1.686351039999999</v>
       </c>
       <c r="Q85">
-        <v>2.821363229999999</v>
+        <v>2.806351039999999</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.3797154187064906</v>
+        <v>0.3999772766377098</v>
       </c>
       <c r="T85">
-        <v>4.000220674292857</v>
+        <v>4.242952511325192</v>
       </c>
       <c r="U85">
         <v>0.07580000000000001</v>
@@ -8295,7 +8295,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>2.365447157854696</v>
+        <v>2.33728707264214</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8303,22 +8303,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.1181175642620335</v>
+        <v>0.1182066073439637</v>
       </c>
       <c r="C86">
-        <v>3.541833193645566</v>
+        <v>3.293334305163079</v>
       </c>
       <c r="D86">
-        <v>22.34683319364557</v>
+        <v>22.33133430516308</v>
       </c>
       <c r="E86">
-        <v>11.672</v>
+        <v>11.905</v>
       </c>
       <c r="F86">
-        <v>19.572</v>
+        <v>19.805</v>
       </c>
       <c r="G86">
         <v>0.767</v>
@@ -8339,28 +8339,28 @@
         <v>3.467499999999999</v>
       </c>
       <c r="M86">
-        <v>1.4835576</v>
+        <v>1.501219</v>
       </c>
       <c r="N86">
-        <v>1.983942399999999</v>
+        <v>1.966280999999999</v>
       </c>
       <c r="O86">
-        <v>0.2975913599999999</v>
+        <v>0.2949421499999999</v>
       </c>
       <c r="P86">
-        <v>1.686351039999999</v>
+        <v>1.671338849999999</v>
       </c>
       <c r="Q86">
-        <v>2.80635104</v>
+        <v>2.791338849999999</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.3999772766377095</v>
+        <v>0.4229407156264245</v>
       </c>
       <c r="T86">
-        <v>4.242952511325188</v>
+        <v>4.518048593295167</v>
       </c>
       <c r="U86">
         <v>0.07580000000000001</v>
@@ -8377,7 +8377,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>2.33728707264214</v>
+        <v>2.30978957766988</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8385,22 +8385,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.1182066073439637</v>
+        <v>0.1182956504258938</v>
       </c>
       <c r="C87">
-        <v>3.293334305163079</v>
+        <v>3.044856900624509</v>
       </c>
       <c r="D87">
-        <v>22.33133430516308</v>
+        <v>22.31585690062451</v>
       </c>
       <c r="E87">
-        <v>11.905</v>
+        <v>12.138</v>
       </c>
       <c r="F87">
-        <v>19.805</v>
+        <v>20.038</v>
       </c>
       <c r="G87">
         <v>0.767</v>
@@ -8421,28 +8421,28 @@
         <v>3.467499999999999</v>
       </c>
       <c r="M87">
-        <v>1.501219</v>
+        <v>1.5188804</v>
       </c>
       <c r="N87">
-        <v>1.966280999999999</v>
+        <v>1.948619599999999</v>
       </c>
       <c r="O87">
-        <v>0.2949421499999999</v>
+        <v>0.2922929399999998</v>
       </c>
       <c r="P87">
-        <v>1.671338849999999</v>
+        <v>1.656326659999999</v>
       </c>
       <c r="Q87">
-        <v>2.791338849999999</v>
+        <v>2.77632666</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.4229407156264245</v>
+        <v>0.4491846458992416</v>
       </c>
       <c r="T87">
-        <v>4.518048593295167</v>
+        <v>4.832444115546569</v>
       </c>
       <c r="U87">
         <v>0.07580000000000001</v>
@@ -8459,7 +8459,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>2.30978957766988</v>
+        <v>2.282931559324881</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8467,22 +8467,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.1182956504258938</v>
+        <v>0.118384693507824</v>
       </c>
       <c r="C88">
-        <v>3.044856900624509</v>
+        <v>2.796400935390515</v>
       </c>
       <c r="D88">
-        <v>22.31585690062451</v>
+        <v>22.30040093539052</v>
       </c>
       <c r="E88">
-        <v>12.138</v>
+        <v>12.371</v>
       </c>
       <c r="F88">
-        <v>20.038</v>
+        <v>20.271</v>
       </c>
       <c r="G88">
         <v>0.767</v>
@@ -8503,28 +8503,28 @@
         <v>3.467499999999999</v>
       </c>
       <c r="M88">
-        <v>1.5188804</v>
+        <v>1.5365418</v>
       </c>
       <c r="N88">
-        <v>1.948619599999999</v>
+        <v>1.930958199999999</v>
       </c>
       <c r="O88">
-        <v>0.2922929399999998</v>
+        <v>0.2896437299999999</v>
       </c>
       <c r="P88">
-        <v>1.656326659999999</v>
+        <v>1.641314469999999</v>
       </c>
       <c r="Q88">
-        <v>2.77632666</v>
+        <v>2.761314469999999</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.4491846458992416</v>
+        <v>0.4794661039063383</v>
       </c>
       <c r="T88">
-        <v>4.832444115546569</v>
+        <v>5.195208179682805</v>
       </c>
       <c r="U88">
         <v>0.07580000000000001</v>
@@ -8541,7 +8541,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>2.282931559324881</v>
+        <v>2.256690966688963</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8549,22 +8549,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.118384693507824</v>
+        <v>0.1184737365897541</v>
       </c>
       <c r="C89">
-        <v>2.796400935390515</v>
+        <v>2.547966364945331</v>
       </c>
       <c r="D89">
-        <v>22.30040093539052</v>
+        <v>22.28496636494533</v>
       </c>
       <c r="E89">
-        <v>12.371</v>
+        <v>12.604</v>
       </c>
       <c r="F89">
-        <v>20.271</v>
+        <v>20.504</v>
       </c>
       <c r="G89">
         <v>0.767</v>
@@ -8585,28 +8585,28 @@
         <v>3.467499999999999</v>
       </c>
       <c r="M89">
-        <v>1.5365418</v>
+        <v>1.5542032</v>
       </c>
       <c r="N89">
-        <v>1.930958199999999</v>
+        <v>1.913296799999999</v>
       </c>
       <c r="O89">
-        <v>0.2896437299999999</v>
+        <v>0.2869945199999999</v>
       </c>
       <c r="P89">
-        <v>1.641314469999999</v>
+        <v>1.626302279999999</v>
       </c>
       <c r="Q89">
-        <v>2.761314469999999</v>
+        <v>2.746302279999999</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.4794661039063383</v>
+        <v>0.5147944715812843</v>
       </c>
       <c r="T89">
-        <v>5.195208179682805</v>
+        <v>5.618432921175079</v>
       </c>
       <c r="U89">
         <v>0.07580000000000001</v>
@@ -8623,7 +8623,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>2.256690966688963</v>
+        <v>2.231046751158406</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8631,22 +8631,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.1184737365897541</v>
+        <v>0.1185627796716843</v>
       </c>
       <c r="C90">
-        <v>2.547966364945331</v>
+        <v>2.29955314489635</v>
       </c>
       <c r="D90">
-        <v>22.28496636494533</v>
+        <v>22.26955314489635</v>
       </c>
       <c r="E90">
-        <v>12.604</v>
+        <v>12.837</v>
       </c>
       <c r="F90">
-        <v>20.504</v>
+        <v>20.737</v>
       </c>
       <c r="G90">
         <v>0.767</v>
@@ -8667,28 +8667,28 @@
         <v>3.467499999999999</v>
       </c>
       <c r="M90">
-        <v>1.5542032</v>
+        <v>1.5718646</v>
       </c>
       <c r="N90">
-        <v>1.913296799999999</v>
+        <v>1.895635399999999</v>
       </c>
       <c r="O90">
-        <v>0.2869945199999999</v>
+        <v>0.2843453099999999</v>
       </c>
       <c r="P90">
-        <v>1.626302279999999</v>
+        <v>1.611290089999999</v>
       </c>
       <c r="Q90">
-        <v>2.746302279999999</v>
+        <v>2.731290089999999</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.5147944715812843</v>
+        <v>0.5565461788334934</v>
       </c>
       <c r="T90">
-        <v>5.618432921175079</v>
+        <v>6.118607615665948</v>
       </c>
       <c r="U90">
         <v>0.07580000000000001</v>
@@ -8705,7 +8705,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>2.231046751158406</v>
+        <v>2.205978810134154</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8713,22 +8713,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.1185627796716843</v>
+        <v>0.1186518227536144</v>
       </c>
       <c r="C91">
-        <v>2.29955314489635</v>
+        <v>2.051161230973694</v>
       </c>
       <c r="D91">
-        <v>22.26955314489635</v>
+        <v>22.2541612309737</v>
       </c>
       <c r="E91">
-        <v>12.837</v>
+        <v>13.07</v>
       </c>
       <c r="F91">
-        <v>20.737</v>
+        <v>20.97</v>
       </c>
       <c r="G91">
         <v>0.767</v>
@@ -8749,28 +8749,28 @@
         <v>3.467499999999999</v>
       </c>
       <c r="M91">
-        <v>1.5718646</v>
+        <v>1.589526</v>
       </c>
       <c r="N91">
-        <v>1.895635399999999</v>
+        <v>1.877973999999999</v>
       </c>
       <c r="O91">
-        <v>0.2843453099999999</v>
+        <v>0.2816960999999998</v>
       </c>
       <c r="P91">
-        <v>1.611290089999999</v>
+        <v>1.596277899999999</v>
       </c>
       <c r="Q91">
-        <v>2.731290089999999</v>
+        <v>2.7162779</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.5565461788334934</v>
+        <v>0.6066482275361443</v>
       </c>
       <c r="T91">
-        <v>6.118607615665948</v>
+        <v>6.718817249054992</v>
       </c>
       <c r="U91">
         <v>0.07580000000000001</v>
@@ -8787,7 +8787,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>2.205978810134154</v>
+        <v>2.181467934465998</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8795,22 +8795,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.1186518227536144</v>
+        <v>0.1187408658355446</v>
       </c>
       <c r="C92">
-        <v>2.051161230973694</v>
+        <v>1.802790579029796</v>
       </c>
       <c r="D92">
-        <v>22.2541612309737</v>
+        <v>22.2387905790298</v>
       </c>
       <c r="E92">
-        <v>13.07</v>
+        <v>13.303</v>
       </c>
       <c r="F92">
-        <v>20.97</v>
+        <v>21.203</v>
       </c>
       <c r="G92">
         <v>0.767</v>
@@ -8831,28 +8831,28 @@
         <v>3.467499999999999</v>
       </c>
       <c r="M92">
-        <v>1.589526</v>
+        <v>1.6071874</v>
       </c>
       <c r="N92">
-        <v>1.877973999999999</v>
+        <v>1.860312599999999</v>
       </c>
       <c r="O92">
-        <v>0.2816960999999998</v>
+        <v>0.2790468899999998</v>
       </c>
       <c r="P92">
-        <v>1.596277899999999</v>
+        <v>1.581265709999999</v>
       </c>
       <c r="Q92">
-        <v>2.7162779</v>
+        <v>2.701265709999999</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.6066482275361443</v>
+        <v>0.6678840648393842</v>
       </c>
       <c r="T92">
-        <v>6.718817249054992</v>
+        <v>7.452406800974933</v>
       </c>
       <c r="U92">
         <v>0.07580000000000001</v>
@@ -8869,7 +8869,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>2.181467934465998</v>
+        <v>2.157495759361975</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8877,22 +8877,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.1187408658355446</v>
+        <v>0.1188299089174747</v>
       </c>
       <c r="C93">
-        <v>1.802790579029796</v>
+        <v>1.554441145038968</v>
       </c>
       <c r="D93">
-        <v>22.2387905790298</v>
+        <v>22.22344114503897</v>
       </c>
       <c r="E93">
-        <v>13.303</v>
+        <v>13.536</v>
       </c>
       <c r="F93">
-        <v>21.203</v>
+        <v>21.436</v>
       </c>
       <c r="G93">
         <v>0.767</v>
@@ -8913,28 +8913,28 @@
         <v>3.467499999999999</v>
       </c>
       <c r="M93">
-        <v>1.6071874</v>
+        <v>1.6248488</v>
       </c>
       <c r="N93">
-        <v>1.860312599999999</v>
+        <v>1.842651199999999</v>
       </c>
       <c r="O93">
-        <v>0.2790468899999998</v>
+        <v>0.2763976799999999</v>
       </c>
       <c r="P93">
-        <v>1.581265709999999</v>
+        <v>1.566253519999999</v>
       </c>
       <c r="Q93">
-        <v>2.701265709999999</v>
+        <v>2.686253519999999</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.6678840648393842</v>
+        <v>0.7444288614684343</v>
       </c>
       <c r="T93">
-        <v>7.452406800974933</v>
+        <v>8.369393740874862</v>
       </c>
       <c r="U93">
         <v>0.07580000000000001</v>
@@ -8951,7 +8951,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>2.157495759361975</v>
+        <v>2.134044718499346</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8959,22 +8959,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.1188299089174747</v>
+        <v>0.1189189519994049</v>
       </c>
       <c r="C94">
-        <v>1.554441145038968</v>
+        <v>1.306112885096987</v>
       </c>
       <c r="D94">
-        <v>22.22344114503897</v>
+        <v>22.20811288509699</v>
       </c>
       <c r="E94">
-        <v>13.536</v>
+        <v>13.769</v>
       </c>
       <c r="F94">
-        <v>21.436</v>
+        <v>21.669</v>
       </c>
       <c r="G94">
         <v>0.767</v>
@@ -8995,28 +8995,28 @@
         <v>3.467499999999999</v>
       </c>
       <c r="M94">
-        <v>1.6248488</v>
+        <v>1.6425102</v>
       </c>
       <c r="N94">
-        <v>1.842651199999999</v>
+        <v>1.824989799999999</v>
       </c>
       <c r="O94">
-        <v>0.2763976799999999</v>
+        <v>0.2737484699999999</v>
       </c>
       <c r="P94">
-        <v>1.566253519999999</v>
+        <v>1.551241329999999</v>
       </c>
       <c r="Q94">
-        <v>2.686253519999999</v>
+        <v>2.671241329999999</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.7444288614684343</v>
+        <v>0.8428435999914986</v>
       </c>
       <c r="T94">
-        <v>8.369393740874862</v>
+        <v>9.548376949317626</v>
       </c>
       <c r="U94">
         <v>0.07580000000000001</v>
@@ -9033,7 +9033,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>2.134044718499346</v>
+        <v>2.111098001096126</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9041,22 +9041,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.1189189519994049</v>
+        <v>0.119007995081335</v>
       </c>
       <c r="C95">
-        <v>1.306112885096987</v>
+        <v>1.057805755420674</v>
       </c>
       <c r="D95">
-        <v>22.20811288509699</v>
+        <v>22.19280575542068</v>
       </c>
       <c r="E95">
-        <v>13.769</v>
+        <v>14.002</v>
       </c>
       <c r="F95">
-        <v>21.669</v>
+        <v>21.902</v>
       </c>
       <c r="G95">
         <v>0.767</v>
@@ -9077,28 +9077,28 @@
         <v>3.467499999999999</v>
       </c>
       <c r="M95">
-        <v>1.6425102</v>
+        <v>1.6601716</v>
       </c>
       <c r="N95">
-        <v>1.824989799999999</v>
+        <v>1.807328399999999</v>
       </c>
       <c r="O95">
-        <v>0.2737484699999999</v>
+        <v>0.2710992599999998</v>
       </c>
       <c r="P95">
-        <v>1.551241329999999</v>
+        <v>1.536229139999999</v>
       </c>
       <c r="Q95">
-        <v>2.671241329999999</v>
+        <v>2.656229139999999</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.8428435999914986</v>
+        <v>0.9740632513555844</v>
       </c>
       <c r="T95">
-        <v>9.548376949317626</v>
+        <v>11.12035456057465</v>
       </c>
       <c r="U95">
         <v>0.07580000000000001</v>
@@ -9115,7 +9115,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>2.111098001096126</v>
+        <v>2.088639511722763</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9123,22 +9123,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.119007995081335</v>
+        <v>0.1190970381632652</v>
       </c>
       <c r="C96">
-        <v>1.057805755420674</v>
+        <v>0.8095197123474804</v>
       </c>
       <c r="D96">
-        <v>22.19280575542068</v>
+        <v>22.17751971234748</v>
       </c>
       <c r="E96">
-        <v>14.002</v>
+        <v>14.235</v>
       </c>
       <c r="F96">
-        <v>21.902</v>
+        <v>22.135</v>
       </c>
       <c r="G96">
         <v>0.767</v>
@@ -9159,28 +9159,28 @@
         <v>3.467499999999999</v>
       </c>
       <c r="M96">
-        <v>1.6601716</v>
+        <v>1.677833</v>
       </c>
       <c r="N96">
-        <v>1.807328399999999</v>
+        <v>1.789666999999999</v>
       </c>
       <c r="O96">
-        <v>0.2710992599999998</v>
+        <v>0.2684500499999998</v>
       </c>
       <c r="P96">
-        <v>1.536229139999999</v>
+        <v>1.521216949999999</v>
       </c>
       <c r="Q96">
-        <v>2.656229139999999</v>
+        <v>2.64121695</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.9740632513555844</v>
+        <v>1.157770763265305</v>
       </c>
       <c r="T96">
-        <v>11.12035456057465</v>
+        <v>13.32112321633448</v>
       </c>
       <c r="U96">
         <v>0.07580000000000001</v>
@@ -9197,7 +9197,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>2.088639511722763</v>
+        <v>2.066653832651998</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9205,22 +9205,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.1190970381632652</v>
+        <v>0.1191860812451953</v>
       </c>
       <c r="C97">
-        <v>0.8095197123474804</v>
+        <v>0.5612547123350744</v>
       </c>
       <c r="D97">
-        <v>22.17751971234748</v>
+        <v>22.16225471233508</v>
       </c>
       <c r="E97">
-        <v>14.235</v>
+        <v>14.468</v>
       </c>
       <c r="F97">
-        <v>22.135</v>
+        <v>22.368</v>
       </c>
       <c r="G97">
         <v>0.767</v>
@@ -9241,28 +9241,28 @@
         <v>3.467499999999999</v>
       </c>
       <c r="M97">
-        <v>1.677833</v>
+        <v>1.6954944</v>
       </c>
       <c r="N97">
-        <v>1.789666999999999</v>
+        <v>1.772005599999999</v>
       </c>
       <c r="O97">
-        <v>0.2684500499999998</v>
+        <v>0.2658008399999999</v>
       </c>
       <c r="P97">
-        <v>1.521216949999999</v>
+        <v>1.506204759999999</v>
       </c>
       <c r="Q97">
-        <v>2.64121695</v>
+        <v>2.626204759999999</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>1.157770763265305</v>
+        <v>1.433332031129885</v>
       </c>
       <c r="T97">
-        <v>13.32112321633448</v>
+        <v>16.62227619997423</v>
       </c>
       <c r="U97">
         <v>0.07580000000000001</v>
@@ -9279,7 +9279,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>2.066653832651998</v>
+        <v>2.045126188561873</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9287,22 +9287,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.1191860812451953</v>
+        <v>0.1192751243271255</v>
       </c>
       <c r="C98">
-        <v>0.561254712335078</v>
+        <v>0.3130107119609207</v>
       </c>
       <c r="D98">
-        <v>22.16225471233508</v>
+        <v>22.14701071196092</v>
       </c>
       <c r="E98">
-        <v>14.468</v>
+        <v>14.701</v>
       </c>
       <c r="F98">
-        <v>22.368</v>
+        <v>22.601</v>
       </c>
       <c r="G98">
         <v>0.767</v>
@@ -9323,28 +9323,28 @@
         <v>3.467499999999999</v>
       </c>
       <c r="M98">
-        <v>1.6954944</v>
+        <v>1.7131558</v>
       </c>
       <c r="N98">
-        <v>1.772005599999999</v>
+        <v>1.754344199999999</v>
       </c>
       <c r="O98">
-        <v>0.2658008399999999</v>
+        <v>0.2631516299999999</v>
       </c>
       <c r="P98">
-        <v>1.506204759999999</v>
+        <v>1.491192569999999</v>
       </c>
       <c r="Q98">
-        <v>2.626204759999999</v>
+        <v>2.61119257</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>1.433332031129882</v>
+        <v>1.892600810904181</v>
       </c>
       <c r="T98">
-        <v>16.62227619997418</v>
+        <v>22.12419783937374</v>
       </c>
       <c r="U98">
         <v>0.07580000000000001</v>
@@ -9361,7 +9361,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>2.045126188561873</v>
+        <v>2.02404241342206</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9369,22 +9369,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.1192751243271255</v>
+        <v>0.1193641674090556</v>
       </c>
       <c r="C99">
-        <v>0.3130107119609207</v>
+        <v>0.06478766792187329</v>
       </c>
       <c r="D99">
-        <v>22.14701071196092</v>
+        <v>22.13178766792187</v>
       </c>
       <c r="E99">
-        <v>14.701</v>
+        <v>14.934</v>
       </c>
       <c r="F99">
-        <v>22.601</v>
+        <v>22.834</v>
       </c>
       <c r="G99">
         <v>0.767</v>
@@ -9405,28 +9405,28 @@
         <v>3.467499999999999</v>
       </c>
       <c r="M99">
-        <v>1.7131558</v>
+        <v>1.7308172</v>
       </c>
       <c r="N99">
-        <v>1.754344199999999</v>
+        <v>1.736682799999999</v>
       </c>
       <c r="O99">
-        <v>0.2631516299999999</v>
+        <v>0.2605024199999998</v>
       </c>
       <c r="P99">
-        <v>1.491192569999999</v>
+        <v>1.476180379999999</v>
       </c>
       <c r="Q99">
-        <v>2.61119257</v>
+        <v>2.596180379999999</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.892600810904181</v>
+        <v>2.811138370452778</v>
       </c>
       <c r="T99">
-        <v>22.12419783937374</v>
+        <v>33.12804111817285</v>
       </c>
       <c r="U99">
         <v>0.07580000000000001</v>
@@ -9443,7 +9443,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>2.02404241342206</v>
+        <v>2.003388919407548</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9451,22 +9451,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.1193641674090556</v>
+        <v>0.1314025104909858</v>
       </c>
       <c r="C100">
-        <v>0.06478766792187329</v>
+        <v>-2.05002906206149</v>
       </c>
       <c r="D100">
-        <v>22.13178766792187</v>
+        <v>20.24997093793851</v>
       </c>
       <c r="E100">
-        <v>14.934</v>
+        <v>15.167</v>
       </c>
       <c r="F100">
-        <v>22.834</v>
+        <v>23.067</v>
       </c>
       <c r="G100">
         <v>0.767</v>
@@ -9487,129 +9487,47 @@
         <v>3.467499999999999</v>
       </c>
       <c r="M100">
-        <v>1.7308172</v>
+        <v>2.07603</v>
       </c>
       <c r="N100">
-        <v>1.736682799999999</v>
+        <v>1.39147</v>
       </c>
       <c r="O100">
-        <v>0.2605024199999998</v>
+        <v>0.2087204999999999</v>
       </c>
       <c r="P100">
-        <v>1.476180379999999</v>
+        <v>1.1827495</v>
       </c>
       <c r="Q100">
-        <v>2.596180379999999</v>
+        <v>2.3027495</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>2.811138370452778</v>
+        <v>5.566751049098571</v>
       </c>
       <c r="T100">
-        <v>33.12804111817285</v>
+        <v>66.13957095457016</v>
       </c>
       <c r="U100">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V100">
         <v>0.15</v>
       </c>
       <c r="W100">
-        <v>0.06443</v>
+        <v>0.0765</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y100">
-        <v>2.003388919407548</v>
+        <v>1.670255246793158</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.1314025104909858</v>
-      </c>
-      <c r="C101">
-        <v>-2.05002906206149</v>
-      </c>
-      <c r="D101">
-        <v>20.24997093793851</v>
-      </c>
-      <c r="E101">
-        <v>15.167</v>
-      </c>
-      <c r="F101">
-        <v>23.067</v>
-      </c>
-      <c r="G101">
-        <v>0.767</v>
-      </c>
-      <c r="H101">
-        <v>15.4</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>4.587499999999999</v>
-      </c>
-      <c r="K101">
-        <v>1.12</v>
-      </c>
-      <c r="L101">
-        <v>3.467499999999999</v>
-      </c>
-      <c r="M101">
-        <v>2.07603</v>
-      </c>
-      <c r="N101">
-        <v>1.39147</v>
-      </c>
-      <c r="O101">
-        <v>0.2087204999999999</v>
-      </c>
-      <c r="P101">
-        <v>1.1827495</v>
-      </c>
-      <c r="Q101">
-        <v>2.3027495</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>5.566751049098571</v>
-      </c>
-      <c r="T101">
-        <v>66.13957095457016</v>
-      </c>
-      <c r="U101">
-        <v>0.09</v>
-      </c>
-      <c r="V101">
-        <v>0.15</v>
-      </c>
-      <c r="W101">
-        <v>0.0765</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>B3/B-</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>1.670255246793158</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
